--- a/hardware/BodyTempSens_Data.xlsx
+++ b/hardware/BodyTempSens_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daanheetkamp/Desktop/BodyTempSensor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9938FF-DBF0-4546-A7E4-F50F0D6CD99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFC80BE-FF6D-F947-A5FA-7AEC4A821F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="68800" windowHeight="28200" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="4" r:id="rId1"/>
@@ -53,7 +53,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{BFA707CE-F671-9544-9F5A-C67EA3FCE0BA}" name="BodyTempSensor" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/daanheetkamp/Desktop/BodyTempSensor/KiCad/BodyTempSensor.csv" decimal="," thousands="." tab="0" comma="1">
+    <textPr sourceFile="/Users/daanheetkamp/Desktop/BodyTempSensor/KiCad/BodyTempSensor.csv" decimal="," thousands="." tab="0" comma="1">
       <textFields count="9">
         <textField type="text"/>
         <textField/>
@@ -87,7 +87,7 @@
     </textPr>
   </connection>
   <connection id="3" xr16:uid="{31195BEF-B649-334C-9645-97AC65444AD5}" name="LCSC__WM2407090249_20260617034145" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/daanheetkamp/Downloads/LCSC__WM2407090249_20260617034145.csv" decimal="," thousands="." tab="0" comma="1">
+    <textPr sourceFile="/Users/daanheetkamp/Downloads/LCSC__WM2407090249_20260617034145.csv" decimal="," thousands="." tab="0" comma="1">
       <textFields count="13">
         <textField/>
         <textField/>
@@ -106,7 +106,7 @@
     </textPr>
   </connection>
   <connection id="4" xr16:uid="{735BE0DB-D0BD-0E4E-BD5E-880E24239B29}" name="LCSC__WM2509140097_20260617034302" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="10000" sourceFile="/Users/daanheetkamp/Downloads/LCSC__WM2509140097_20260617034302.csv" decimal="," thousands="." tab="0" comma="1">
+    <textPr sourceFile="/Users/daanheetkamp/Downloads/LCSC__WM2509140097_20260617034302.csv" decimal="," thousands="." tab="0" comma="1">
       <textFields count="13">
         <textField/>
         <textField/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="866">
   <si>
     <t>ESP32-C6-MINI-1-N4</t>
   </si>
@@ -926,9 +926,6 @@
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
-    <t>Resistor</t>
-  </si>
-  <si>
     <t>EVQP2B02B</t>
   </si>
   <si>
@@ -1259,9 +1256,6 @@
     <t>Capacitor_SMD:C_0504_1310Metric_Pad0.83x1.28mm_HandSolder</t>
   </si>
   <si>
-    <t>Unpolarized capacitor</t>
-  </si>
-  <si>
     <t>C3,C5,C7,C10,C12,C14,C22,C23,C24,C25,C26</t>
   </si>
   <si>
@@ -1328,9 +1322,6 @@
     <t>10n</t>
   </si>
   <si>
-    <t>25V 10nF X5R ¬±10% 0402</t>
-  </si>
-  <si>
     <t>C28,C30</t>
   </si>
   <si>
@@ -1343,12 +1334,6 @@
     <t>D1,D2,D3</t>
   </si>
   <si>
-    <t>LED_SMD:LED_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
-  </si>
-  <si>
-    <t>Light emitting diode</t>
-  </si>
-  <si>
     <t>IC3</t>
   </si>
   <si>
@@ -1382,12 +1367,6 @@
     <t>Connector_USB:USB_C_Receptacle_GCT_USB4105-xx-A_16P_TopMnt_Horizontal</t>
   </si>
   <si>
-    <t>https://www.usb.org/sites/default/files/documents/usb_type-c.zip</t>
-  </si>
-  <si>
-    <t>USB 2.0-only Type-C Receptacle connector</t>
-  </si>
-  <si>
     <t>TC2030</t>
   </si>
   <si>
@@ -1433,12 +1412,6 @@
     <t>Inductor_SMD:L_0201_0603Metric</t>
   </si>
   <si>
-    <t>LQP03HQ3N5B02</t>
-  </si>
-  <si>
-    <t>3.5 nH 0402</t>
-  </si>
-  <si>
     <t>Inductor_SMD_Wurth:L_Wurth_WE-LQSH-4020</t>
   </si>
   <si>
@@ -1454,18 +1427,9 @@
     <t>2.7nH</t>
   </si>
   <si>
-    <t>LQP03HQ2N7B02</t>
-  </si>
-  <si>
-    <t>2.7 nH 0402</t>
-  </si>
-  <si>
     <t>L5</t>
   </si>
   <si>
-    <t>4.7 nH 0402</t>
-  </si>
-  <si>
     <t>PCB_Lib_ItsNotDaan:WS2812C2020</t>
   </si>
   <si>
@@ -2621,15 +2585,6 @@
     <t>2.64</t>
   </si>
   <si>
-    <t>Gecheckt</t>
-  </si>
-  <si>
-    <t>Ja</t>
-  </si>
-  <si>
-    <t>Nee</t>
-  </si>
-  <si>
     <t>C295941</t>
   </si>
   <si>
@@ -2747,142 +2702,76 @@
     <t>2pF ±0.1pF 50V NP0 0402 (niet op LCSC, zie Farnell)</t>
   </si>
   <si>
-    <t>LCSC Voorraad / Prijs (USD)</t>
-  </si>
-  <si>
-    <t>C512395 | 174k stk | $0.11</t>
-  </si>
-  <si>
-    <t>C2925417 | op voorraad | $0.06</t>
-  </si>
-  <si>
-    <t>C113791 | 500k+ stk | $0.003</t>
-  </si>
-  <si>
-    <t>C82453 | 100k+ stk | $0.007</t>
-  </si>
-  <si>
-    <t>Niet op LCSC — zoek 0402 390nF X5R elders</t>
-  </si>
-  <si>
-    <t>C2992625 | 300k+ stk | $0.005</t>
-  </si>
-  <si>
-    <t>Niet op LCSC — zie KiCad voetafdruk</t>
-  </si>
-  <si>
-    <t>C295917 | 1M+ stk | $0.0006</t>
-  </si>
-  <si>
-    <t>C295941 | op voorraad | $0.006</t>
-  </si>
-  <si>
-    <t>C106861 | op voorraad | $0.0015</t>
-  </si>
-  <si>
-    <t>C361203 | op voorraad | $0.003</t>
-  </si>
-  <si>
-    <t>Niet op LCSC — 1.5pF NP0 0402 zeldzaam</t>
-  </si>
-  <si>
-    <t>C106201 | op voorraad | $0.0006</t>
-  </si>
-  <si>
-    <t>Geen LCSC C# — bestellen bij Farnell/TME</t>
-  </si>
-  <si>
-    <t>C965790 | op voorraad | $0.006</t>
-  </si>
-  <si>
-    <t>C2803242 | 287 stk | $1.03</t>
-  </si>
-  <si>
-    <t>C2803242 | 287 stk | $1.03 (MAIDRVT obsoleet)</t>
-  </si>
-  <si>
-    <t>C42458750 | op voorraad | $2.36</t>
-  </si>
-  <si>
-    <t>C223907 | op voorraad | $0.10</t>
-  </si>
-  <si>
-    <t>TC2030 — order bij Digikey/Mouser</t>
-  </si>
-  <si>
-    <t>BAT connector — type onbekend</t>
-  </si>
-  <si>
-    <t>Conn 2x5 — type onbekend</t>
-  </si>
-  <si>
-    <t>3.5nH inductor — niet op LCSC</t>
-  </si>
-  <si>
-    <t>C135262 | op voorraad | $0.08</t>
-  </si>
-  <si>
-    <t>2.7nH inductor — niet op LCSC</t>
-  </si>
-  <si>
-    <t>4.7uH inductor — niet op LCSC</t>
-  </si>
-  <si>
-    <t>C2976072 | 500k+ stk | $0.009</t>
-  </si>
-  <si>
-    <t>C20917 | 174k stk | $0.04</t>
-  </si>
-  <si>
-    <t>C105873 | 300k+ stk | $0.0005</t>
-  </si>
-  <si>
-    <t>C238338 | op voorraad | $0.0005</t>
-  </si>
-  <si>
-    <t>C705662 | op voorraad | $0.0005</t>
-  </si>
-  <si>
-    <t>C137932 | 142k stk | $0.0003</t>
-  </si>
-  <si>
-    <t>C5159688 | op voorraad | $0.003</t>
-  </si>
-  <si>
-    <t>C138046 | op voorraad | $0.0006</t>
-  </si>
-  <si>
-    <t>C93943 | 1,376k stk | $0.0003</t>
-  </si>
-  <si>
-    <t>C413049 | op voorraad | $0.004</t>
-  </si>
-  <si>
-    <t>C3017744 | op voorraad | $0.002</t>
-  </si>
-  <si>
-    <t>C163810 | op voorraad | $0.0005</t>
-  </si>
-  <si>
-    <t>C106235 | 597k stk | $0.0005</t>
-  </si>
-  <si>
-    <t>Testpunten — geen component nodig</t>
-  </si>
-  <si>
-    <t>C2827654 | op voorraad | $0.007</t>
-  </si>
-  <si>
-    <t>C424093 | op voorraad | $0.09</t>
-  </si>
-  <si>
-    <t>C163219 | op voorraad | $0.06</t>
-  </si>
-  <si>
-    <t>C116490 | 77k stk | $0.12</t>
-  </si>
-  <si>
-    <t>C113671 | op voorraad | $0.037</t>
+    <t>C7393858</t>
+  </si>
+  <si>
+    <t>CAP CER 390nF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>TCC0402X5R394K160AT</t>
+  </si>
+  <si>
+    <t>RES 5.1kΩ ±5% 62.5mW 0402</t>
+  </si>
+  <si>
+    <t>CCTC</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB105</t>
+  </si>
+  <si>
+    <t>C106254</t>
+  </si>
+  <si>
+    <t>CAP CER 1uF 10V X5R 0402</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R8BB103</t>
+  </si>
+  <si>
+    <t>C327025</t>
+  </si>
+  <si>
+    <t>CAP CER 10nF 25V X7R 0402</t>
+  </si>
+  <si>
+    <t>TBT</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0402_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>TCGL0603C3N5SZT</t>
+  </si>
+  <si>
+    <t>450mA 3.5nH 250mΩ Multilayer inductor 0201 Fixed Inductors RoHS</t>
+  </si>
+  <si>
+    <t>C52109755</t>
+  </si>
+  <si>
+    <t>muRata</t>
+  </si>
+  <si>
+    <t>LQG15HS2N7S02D</t>
+  </si>
+  <si>
+    <t>FIXED IND 2.7nH 800mA 120mΩ 0402</t>
+  </si>
+  <si>
+    <t>C77108</t>
+  </si>
+  <si>
+    <t>MLZ1608M4R7WT000</t>
+  </si>
+  <si>
+    <t>FIXED IND 4.7uH 500mΩ 0603</t>
+  </si>
+  <si>
+    <t>C76799</t>
+  </si>
+  <si>
+    <t>TDK</t>
   </si>
 </sst>
 </file>
@@ -3468,10 +3357,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3483,26 +3384,14 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7099,30 +6988,30 @@
       <c r="F1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="N1" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="Y1" s="56" t="s">
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="Y1" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56"/>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
     </row>
     <row r="2" spans="1:47" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -7381,10 +7270,10 @@
       <c r="AH5" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="AJ5" s="47" t="s">
+      <c r="AJ5" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="AK5" s="48"/>
+      <c r="AK5" s="57"/>
       <c r="AM5" t="s">
         <v>233</v>
       </c>
@@ -7805,24 +7694,24 @@
         <f>Y13*AB13</f>
         <v>0.39599999999999996</v>
       </c>
-      <c r="AE13" s="49" t="s">
+      <c r="AE13" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="AF13" s="50"/>
-      <c r="AG13" s="50"/>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-      <c r="AJ13" s="50"/>
-      <c r="AK13" s="51"/>
-      <c r="AO13" s="49" t="s">
+      <c r="AF13" s="54"/>
+      <c r="AG13" s="54"/>
+      <c r="AH13" s="54"/>
+      <c r="AI13" s="54"/>
+      <c r="AJ13" s="54"/>
+      <c r="AK13" s="55"/>
+      <c r="AO13" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="AP13" s="50"/>
-      <c r="AQ13" s="50"/>
-      <c r="AR13" s="50"/>
-      <c r="AS13" s="50"/>
-      <c r="AT13" s="50"/>
-      <c r="AU13" s="51"/>
+      <c r="AP13" s="54"/>
+      <c r="AQ13" s="54"/>
+      <c r="AR13" s="54"/>
+      <c r="AS13" s="54"/>
+      <c r="AT13" s="54"/>
+      <c r="AU13" s="55"/>
     </row>
     <row r="14" spans="1:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="P14" s="4">
@@ -7843,28 +7732,28 @@
         <v>0.86</v>
       </c>
       <c r="AC14" s="4"/>
-      <c r="AE14" s="52" t="s">
+      <c r="AE14" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="AF14" s="53"/>
-      <c r="AG14" s="54"/>
+      <c r="AF14" s="51"/>
+      <c r="AG14" s="58"/>
       <c r="AH14" s="13"/>
-      <c r="AI14" s="52" t="s">
+      <c r="AI14" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="AJ14" s="53"/>
-      <c r="AK14" s="55"/>
-      <c r="AO14" s="52" t="s">
+      <c r="AJ14" s="51"/>
+      <c r="AK14" s="52"/>
+      <c r="AO14" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="AP14" s="53"/>
-      <c r="AQ14" s="54"/>
+      <c r="AP14" s="51"/>
+      <c r="AQ14" s="58"/>
       <c r="AR14" s="13"/>
-      <c r="AS14" s="52" t="s">
+      <c r="AS14" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="AT14" s="53"/>
-      <c r="AU14" s="55"/>
+      <c r="AT14" s="51"/>
+      <c r="AU14" s="52"/>
     </row>
     <row r="15" spans="1:47" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
@@ -7987,50 +7876,50 @@
         <f>J8-(J13/2)</f>
         <v>1.1308825454545455</v>
       </c>
-      <c r="AE19" s="49" t="s">
+      <c r="AE19" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="AF19" s="50"/>
-      <c r="AG19" s="50"/>
-      <c r="AH19" s="50"/>
-      <c r="AI19" s="50"/>
-      <c r="AJ19" s="50"/>
-      <c r="AK19" s="51"/>
-      <c r="AO19" s="49" t="s">
+      <c r="AF19" s="54"/>
+      <c r="AG19" s="54"/>
+      <c r="AH19" s="54"/>
+      <c r="AI19" s="54"/>
+      <c r="AJ19" s="54"/>
+      <c r="AK19" s="55"/>
+      <c r="AO19" s="53" t="s">
         <v>220</v>
       </c>
-      <c r="AP19" s="50"/>
-      <c r="AQ19" s="50"/>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
-      <c r="AT19" s="50"/>
-      <c r="AU19" s="51"/>
+      <c r="AP19" s="54"/>
+      <c r="AQ19" s="54"/>
+      <c r="AR19" s="54"/>
+      <c r="AS19" s="54"/>
+      <c r="AT19" s="54"/>
+      <c r="AU19" s="55"/>
     </row>
     <row r="20" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="AE20" s="52" t="s">
+      <c r="AE20" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="AF20" s="53"/>
-      <c r="AG20" s="54"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="58"/>
       <c r="AH20" s="7"/>
-      <c r="AI20" s="52" t="s">
+      <c r="AI20" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="AJ20" s="53"/>
-      <c r="AK20" s="55"/>
-      <c r="AO20" s="52" t="s">
+      <c r="AJ20" s="51"/>
+      <c r="AK20" s="52"/>
+      <c r="AO20" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="AP20" s="53"/>
-      <c r="AQ20" s="54"/>
+      <c r="AP20" s="51"/>
+      <c r="AQ20" s="58"/>
       <c r="AR20" s="7"/>
-      <c r="AS20" s="52" t="s">
+      <c r="AS20" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="AT20" s="53"/>
-      <c r="AU20" s="55"/>
+      <c r="AT20" s="51"/>
+      <c r="AU20" s="52"/>
     </row>
     <row r="21" spans="6:47" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AE21" s="31" t="s">
@@ -8129,10 +8018,10 @@
     <row r="23" spans="6:47" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="6:47" x14ac:dyDescent="0.2">
-      <c r="AE26" s="47" t="s">
+      <c r="AE26" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="AF26" s="48"/>
+      <c r="AF26" s="57"/>
     </row>
     <row r="27" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AE27" s="28" t="s">
@@ -8190,6 +8079,13 @@
     </sortState>
   </autoFilter>
   <mergeCells count="16">
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AO13:AU13"/>
+    <mergeCell ref="AO14:AQ14"/>
+    <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AO19:AU19"/>
+    <mergeCell ref="AO20:AQ20"/>
+    <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="N1:W1"/>
     <mergeCell ref="Y1:AH1"/>
     <mergeCell ref="AI14:AK14"/>
@@ -8199,13 +8095,6 @@
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AE20:AG20"/>
     <mergeCell ref="AE14:AG14"/>
-    <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="AO13:AU13"/>
-    <mergeCell ref="AO14:AQ14"/>
-    <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AO19:AU19"/>
-    <mergeCell ref="AO20:AQ20"/>
-    <mergeCell ref="AS20:AU20"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AE14">
@@ -8535,36 +8424,36 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" t="s">
         <v>321</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>322</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>323</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>324</v>
-      </c>
-      <c r="G1" t="s">
-        <v>325</v>
       </c>
       <c r="H1" s="2">
         <v>0.5</v>
       </c>
       <c r="J1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K1" t="s">
         <v>322</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>323</v>
-      </c>
-      <c r="L1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -8573,7 +8462,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="I2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J2">
         <f>$H$1/B10</f>
@@ -8590,7 +8479,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2">
         <v>2.4999999999999999E-7</v>
@@ -8603,7 +8492,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="I3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J3">
         <f>J2/24</f>
@@ -8620,7 +8509,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B4" s="2">
         <v>3.4999999999999997E-5</v>
@@ -8635,7 +8524,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B5" s="2">
         <v>1.2999999999999999E-5</v>
@@ -8650,7 +8539,7 @@
     </row>
     <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B6" s="2">
         <v>1.1E-4</v>
@@ -8663,7 +8552,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="I6" s="46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J6" s="46"/>
     </row>
@@ -8682,13 +8571,13 @@
       </c>
       <c r="E7" s="2"/>
       <c r="I7" s="46" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" s="2">
         <v>6.7000000000000002E-5</v>
@@ -8701,23 +8590,23 @@
       </c>
       <c r="E8" s="2"/>
       <c r="I8" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="s">
         <v>322</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>323</v>
-      </c>
-      <c r="D9" t="s">
-        <v>324</v>
       </c>
       <c r="E9" s="2"/>
       <c r="I9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J9">
         <f>$H$1/0.012</f>
@@ -8756,7 +8645,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8795,36 +8684,36 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" t="s">
         <v>321</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>322</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>323</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>324</v>
-      </c>
-      <c r="G19" t="s">
-        <v>325</v>
       </c>
       <c r="H19" s="2">
         <v>0.5</v>
       </c>
       <c r="J19" t="s">
+        <v>321</v>
+      </c>
+      <c r="K19" t="s">
         <v>322</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>323</v>
-      </c>
-      <c r="L19" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -8833,7 +8722,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="I20" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J20" s="2">
         <f>$H$1/B28</f>
@@ -8850,7 +8739,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B21" s="2">
         <v>2.4999999999999999E-7</v>
@@ -8863,7 +8752,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="I21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J21">
         <f>J20/24</f>
@@ -8880,7 +8769,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B22" s="2">
         <v>3.4999999999999997E-5</v>
@@ -8895,7 +8784,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B23" s="2">
         <v>1.2999999999999999E-5</v>
@@ -8910,7 +8799,7 @@
     </row>
     <row r="24" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B24" s="2">
         <v>1.0000000000000001E-5</v>
@@ -8923,7 +8812,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="I24" s="46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J24" s="46"/>
     </row>
@@ -8942,13 +8831,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="I25" s="46" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B26" s="2">
         <v>6.7000000000000002E-5</v>
@@ -8961,23 +8850,23 @@
       </c>
       <c r="E26" s="2"/>
       <c r="I26" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" t="s">
         <v>322</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>323</v>
-      </c>
-      <c r="D27" t="s">
-        <v>324</v>
       </c>
       <c r="E27" s="2"/>
       <c r="I27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J27">
         <f>$H$1/0.012</f>
@@ -9016,7 +8905,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -9066,7 +8955,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -9090,7 +8979,7 @@
     </row>
     <row r="2" spans="1:20" s="35" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -9145,19 +9034,19 @@
         <v>237</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>240</v>
       </c>
       <c r="F4" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="G4" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="H4" s="39" t="s">
         <v>274</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>275</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>236</v>
@@ -9182,10 +9071,10 @@
         <v>244</v>
       </c>
       <c r="C5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" t="s">
         <v>276</v>
-      </c>
-      <c r="D5" t="s">
-        <v>277</v>
       </c>
       <c r="E5">
         <v>21</v>
@@ -9198,10 +9087,10 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="H5" t="s">
+        <v>277</v>
+      </c>
+      <c r="I5" t="s">
         <v>278</v>
-      </c>
-      <c r="I5" t="s">
-        <v>279</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
@@ -9223,10 +9112,10 @@
         <v>245</v>
       </c>
       <c r="C6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" t="s">
         <v>280</v>
-      </c>
-      <c r="D6" t="s">
-        <v>281</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -9239,10 +9128,10 @@
         <v>1.4E-2</v>
       </c>
       <c r="H6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -9264,7 +9153,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -9280,10 +9169,10 @@
         <v>7.8E-2</v>
       </c>
       <c r="H7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
@@ -9305,10 +9194,10 @@
         <v>246</v>
       </c>
       <c r="C8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" t="s">
         <v>285</v>
-      </c>
-      <c r="D8" t="s">
-        <v>286</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -9321,10 +9210,10 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -9346,10 +9235,10 @@
         <v>247</v>
       </c>
       <c r="C9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" t="s">
         <v>288</v>
-      </c>
-      <c r="D9" t="s">
-        <v>289</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -9362,10 +9251,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I9" t="s">
         <v>290</v>
-      </c>
-      <c r="I9" t="s">
-        <v>291</v>
       </c>
       <c r="J9"/>
       <c r="K9"/>
@@ -9384,13 +9273,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" t="s">
         <v>292</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>293</v>
-      </c>
-      <c r="D10" t="s">
-        <v>294</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -9403,10 +9292,10 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -9428,10 +9317,10 @@
         <v>249</v>
       </c>
       <c r="C11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D11" t="s">
         <v>296</v>
-      </c>
-      <c r="D11" t="s">
-        <v>297</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -9444,10 +9333,10 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="H11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J11"/>
       <c r="K11"/>
@@ -9466,13 +9355,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D12" t="s">
         <v>299</v>
-      </c>
-      <c r="D12" t="s">
-        <v>300</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -9485,10 +9374,10 @@
         <v>0.79500000000000004</v>
       </c>
       <c r="H12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -9507,13 +9396,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -9526,10 +9415,10 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="H13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J13"/>
       <c r="K13"/>
@@ -9548,13 +9437,13 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" t="s">
         <v>304</v>
-      </c>
-      <c r="D14" t="s">
-        <v>305</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -9567,10 +9456,10 @@
         <v>1.03</v>
       </c>
       <c r="H14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J14"/>
       <c r="K14"/>
@@ -9589,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C15" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" t="s">
         <v>307</v>
-      </c>
-      <c r="D15" t="s">
-        <v>308</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -9608,10 +9497,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J15"/>
       <c r="K15"/>
@@ -9630,13 +9519,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -9649,10 +9538,10 @@
         <v>0.35</v>
       </c>
       <c r="H16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J16"/>
       <c r="K16"/>
@@ -9671,13 +9560,13 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -9690,10 +9579,10 @@
         <v>0.123</v>
       </c>
       <c r="H17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J17"/>
       <c r="K17"/>
@@ -9712,13 +9601,13 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C18" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" t="s">
         <v>314</v>
-      </c>
-      <c r="D18" t="s">
-        <v>315</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -9731,10 +9620,10 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="H18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J18"/>
       <c r="K18"/>
@@ -9756,10 +9645,10 @@
         <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -9772,10 +9661,10 @@
         <v>5.5E-2</v>
       </c>
       <c r="H19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J19"/>
       <c r="K19"/>
@@ -9813,7 +9702,7 @@
     </row>
     <row r="21" spans="1:20" s="36" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B21" s="44"/>
       <c r="C21" s="44"/>
@@ -9840,7 +9729,7 @@
     </row>
     <row r="22" spans="1:20" s="36" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B22" s="44"/>
       <c r="C22" s="44"/>
@@ -10891,7 +10780,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -10908,7 +10797,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B1" t="s">
         <v>240</v>
@@ -10917,10 +10806,10 @@
         <v>13</v>
       </c>
       <c r="D1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E1" t="s">
         <v>338</v>
-      </c>
-      <c r="E1" t="s">
-        <v>339</v>
       </c>
       <c r="F1" t="s">
         <v>97</v>
@@ -10929,1366 +10818,1184 @@
         <v>98</v>
       </c>
       <c r="H1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I1" t="s">
         <v>237</v>
       </c>
-      <c r="J1" s="40" t="s">
-        <v>815</v>
-      </c>
-      <c r="K1" s="40" t="s">
-        <v>857</v>
-      </c>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>341</v>
+        <v>159</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="F2" t="s">
-        <v>344</v>
+        <v>840</v>
       </c>
       <c r="G2" t="s">
-        <v>345</v>
+        <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>840</v>
       </c>
       <c r="I2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J2" t="s">
-        <v>816</v>
-      </c>
-      <c r="K2" t="s">
-        <v>858</v>
+        <v>841</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>348</v>
+        <v>456</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>457</v>
       </c>
       <c r="D3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E3" t="s">
-        <v>351</v>
+        <v>426</v>
       </c>
       <c r="F3" t="s">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G3" t="s">
-        <v>353</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>349</v>
+        <v>815</v>
       </c>
       <c r="I3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J3" t="s">
         <v>816</v>
-      </c>
-      <c r="K3" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>152</v>
+        <v>369</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F4" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="G4" t="s">
-        <v>357</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="I4" t="s">
-        <v>359</v>
-      </c>
-      <c r="J4" t="s">
-        <v>816</v>
-      </c>
-      <c r="K4" t="s">
-        <v>860</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="F5" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="I5" t="s">
-        <v>374</v>
-      </c>
-      <c r="J5" t="s">
-        <v>816</v>
-      </c>
-      <c r="K5" t="s">
-        <v>861</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="D6" t="s">
-        <v>355</v>
-      </c>
-      <c r="J6" t="s">
-        <v>817</v>
-      </c>
-      <c r="K6" t="s">
-        <v>862</v>
+        <v>426</v>
+      </c>
+      <c r="F6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H6" t="s">
+        <v>452</v>
+      </c>
+      <c r="I6" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="D7" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F7" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="G7" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="H7" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="I7" t="s">
-        <v>381</v>
-      </c>
-      <c r="J7" t="s">
-        <v>816</v>
-      </c>
-      <c r="K7" t="s">
-        <v>863</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>153</v>
+        <v>391</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>360</v>
+        <v>393</v>
+      </c>
+      <c r="E8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" t="s">
+        <v>806</v>
+      </c>
+      <c r="G8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H8" t="s">
+        <v>392</v>
       </c>
       <c r="I8" t="s">
-        <v>361</v>
-      </c>
-      <c r="J8" t="s">
-        <v>817</v>
-      </c>
-      <c r="K8" t="s">
-        <v>864</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>382</v>
+        <v>256</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>465</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>466</v>
+      </c>
+      <c r="E9" t="s">
+        <v>467</v>
+      </c>
+      <c r="F9" t="s">
+        <v>632</v>
+      </c>
+      <c r="G9" t="s">
+        <v>780</v>
+      </c>
+      <c r="H9" t="s">
+        <v>633</v>
       </c>
       <c r="I9" t="s">
-        <v>384</v>
-      </c>
-      <c r="J9" t="s">
-        <v>816</v>
-      </c>
-      <c r="K9" t="s">
-        <v>865</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>428</v>
       </c>
       <c r="D10" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="F10" t="s">
-        <v>818</v>
+        <v>429</v>
       </c>
       <c r="G10" t="s">
-        <v>447</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>819</v>
+        <v>430</v>
       </c>
       <c r="I10" t="s">
-        <v>848</v>
-      </c>
-      <c r="J10" t="s">
-        <v>817</v>
-      </c>
-      <c r="K10" t="s">
-        <v>866</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F11" t="s">
-        <v>849</v>
+        <v>361</v>
       </c>
       <c r="G11" t="s">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>850</v>
+        <v>362</v>
       </c>
       <c r="I11" t="s">
-        <v>851</v>
-      </c>
-      <c r="J11" t="s">
-        <v>817</v>
-      </c>
-      <c r="K11" t="s">
-        <v>867</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>362</v>
+        <v>432</v>
       </c>
       <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>470</v>
       </c>
       <c r="D12" t="s">
-        <v>355</v>
+        <v>426</v>
       </c>
       <c r="F12" t="s">
-        <v>363</v>
+        <v>606</v>
       </c>
       <c r="G12" t="s">
-        <v>4</v>
+        <v>608</v>
       </c>
       <c r="H12" t="s">
-        <v>364</v>
+        <v>607</v>
       </c>
       <c r="I12" t="s">
-        <v>365</v>
-      </c>
-      <c r="J12" t="s">
-        <v>816</v>
-      </c>
-      <c r="K12" t="s">
-        <v>868</v>
+        <v>837</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>375</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>355</v>
+        <v>354</v>
+      </c>
+      <c r="F13" t="s">
+        <v>376</v>
+      </c>
+      <c r="G13" t="s">
+        <v>377</v>
+      </c>
+      <c r="H13" t="s">
+        <v>378</v>
       </c>
       <c r="I13" t="s">
-        <v>367</v>
-      </c>
-      <c r="J13" t="s">
-        <v>817</v>
-      </c>
-      <c r="K13" t="s">
-        <v>869</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>368</v>
+        <v>175</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>369</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>355</v>
+        <v>418</v>
+      </c>
+      <c r="E14" t="s">
+        <v>419</v>
       </c>
       <c r="F14" t="s">
-        <v>853</v>
+        <v>316</v>
       </c>
       <c r="G14" t="s">
-        <v>4</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>820</v>
+        <v>420</v>
       </c>
       <c r="I14" t="s">
-        <v>854</v>
-      </c>
-      <c r="J14" t="s">
-        <v>817</v>
-      </c>
-      <c r="K14" t="s">
-        <v>870</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>159</v>
+        <v>382</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F15" t="s">
-        <v>855</v>
+        <v>803</v>
       </c>
       <c r="G15" t="s">
-        <v>4</v>
+        <v>435</v>
       </c>
       <c r="H15" t="s">
-        <v>855</v>
+        <v>804</v>
       </c>
       <c r="I15" t="s">
-        <v>856</v>
-      </c>
-      <c r="J15" t="s">
-        <v>817</v>
-      </c>
-      <c r="K15" t="s">
-        <v>871</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>235</v>
+        <v>348</v>
       </c>
       <c r="D16" t="s">
-        <v>389</v>
+        <v>349</v>
+      </c>
+      <c r="E16" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16" t="s">
+        <v>351</v>
+      </c>
+      <c r="G16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H16" t="s">
+        <v>348</v>
       </c>
       <c r="I16" t="s">
-        <v>390</v>
-      </c>
-      <c r="J16" t="s">
-        <v>817</v>
-      </c>
-      <c r="K16" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>391</v>
+        <v>254</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>392</v>
+        <v>462</v>
       </c>
       <c r="E17" t="s">
-        <v>393</v>
+        <v>463</v>
       </c>
       <c r="F17" t="s">
-        <v>305</v>
+        <v>674</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>675</v>
       </c>
       <c r="H17" t="s">
-        <v>256</v>
+        <v>23</v>
       </c>
       <c r="I17" t="s">
-        <v>842</v>
-      </c>
-      <c r="J17" t="s">
-        <v>817</v>
-      </c>
-      <c r="K17" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>394</v>
+        <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E18" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I18" t="s">
-        <v>844</v>
-      </c>
-      <c r="J18" t="s">
-        <v>817</v>
-      </c>
-      <c r="K18" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D19" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="E19" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F19" t="s">
-        <v>821</v>
+        <v>304</v>
       </c>
       <c r="G19" t="s">
-        <v>254</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>397</v>
+        <v>255</v>
       </c>
       <c r="I19" t="s">
-        <v>822</v>
-      </c>
-      <c r="J19" t="s">
-        <v>817</v>
-      </c>
-      <c r="K19" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>169</v>
+        <v>440</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="D20" t="s">
-        <v>401</v>
-      </c>
-      <c r="E20" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
-        <v>627</v>
+        <v>808</v>
+      </c>
+      <c r="G20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" t="s">
+        <v>809</v>
       </c>
       <c r="I20" t="s">
-        <v>403</v>
-      </c>
-      <c r="J20" t="s">
-        <v>817</v>
-      </c>
-      <c r="K20" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
-      </c>
-      <c r="E21" t="s">
-        <v>406</v>
-      </c>
-      <c r="I21" t="s">
-        <v>407</v>
-      </c>
-      <c r="J21" t="s">
-        <v>817</v>
-      </c>
-      <c r="K21" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>521</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>616</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>423</v>
+      </c>
+      <c r="E22" t="s">
+        <v>424</v>
+      </c>
+      <c r="F22" t="s">
+        <v>824</v>
+      </c>
+      <c r="G22" t="s">
+        <v>825</v>
+      </c>
+      <c r="H22" t="s">
+        <v>826</v>
+      </c>
+      <c r="I22" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>426</v>
+      </c>
+      <c r="F23" t="s">
+        <v>434</v>
+      </c>
+      <c r="G23" t="s">
+        <v>435</v>
+      </c>
+      <c r="H23" t="s">
+        <v>436</v>
+      </c>
+      <c r="I23" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
-        <v>409</v>
-      </c>
-      <c r="D22" t="s">
-        <v>410</v>
-      </c>
-      <c r="I22" t="s">
-        <v>411</v>
-      </c>
-      <c r="J22" t="s">
-        <v>817</v>
-      </c>
-      <c r="K22" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>413</v>
-      </c>
-      <c r="D23" t="s">
-        <v>414</v>
-      </c>
-      <c r="I23" t="s">
-        <v>415</v>
-      </c>
-      <c r="J23" t="s">
-        <v>817</v>
-      </c>
-      <c r="K23" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
       <c r="C24" t="s">
-        <v>417</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>418</v>
+        <v>469</v>
+      </c>
+      <c r="E24" t="s">
+        <v>470</v>
+      </c>
+      <c r="F24" t="s">
+        <v>309</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>419</v>
+        <v>261</v>
       </c>
       <c r="I24" t="s">
-        <v>420</v>
-      </c>
-      <c r="J24" t="s">
-        <v>817</v>
-      </c>
-      <c r="K24" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>248</v>
+        <v>454</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>455</v>
       </c>
       <c r="D25" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F25" t="s">
-        <v>294</v>
+        <v>831</v>
       </c>
       <c r="G25" t="s">
-        <v>422</v>
+        <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>292</v>
+        <v>813</v>
       </c>
       <c r="I25" t="s">
-        <v>423</v>
-      </c>
-      <c r="J25" t="s">
-        <v>816</v>
-      </c>
-      <c r="K25" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="D26" t="s">
-        <v>418</v>
+        <v>426</v>
+      </c>
+      <c r="F26" t="s">
+        <v>830</v>
+      </c>
+      <c r="G26" t="s">
+        <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>426</v>
+        <v>811</v>
       </c>
       <c r="I26" t="s">
-        <v>427</v>
-      </c>
-      <c r="J26" t="s">
-        <v>817</v>
-      </c>
-      <c r="K26" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>428</v>
+        <v>248</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>418</v>
+        <v>412</v>
+      </c>
+      <c r="F27" t="s">
+        <v>293</v>
+      </c>
+      <c r="G27" t="s">
+        <v>413</v>
+      </c>
+      <c r="H27" t="s">
+        <v>291</v>
       </c>
       <c r="I27" t="s">
-        <v>429</v>
-      </c>
-      <c r="J27" t="s">
-        <v>817</v>
-      </c>
-      <c r="K27" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="D28" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="E28" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="F28" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="G28" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>432</v>
+        <v>264</v>
       </c>
       <c r="I28" t="s">
-        <v>433</v>
-      </c>
-      <c r="J28" t="s">
-        <v>816</v>
-      </c>
-      <c r="K28" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>434</v>
+        <v>152</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>435</v>
-      </c>
-      <c r="E29" t="s">
-        <v>436</v>
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>354</v>
       </c>
       <c r="F29" t="s">
-        <v>839</v>
+        <v>355</v>
       </c>
       <c r="G29" t="s">
-        <v>840</v>
+        <v>356</v>
       </c>
       <c r="H29" t="s">
-        <v>841</v>
+        <v>357</v>
       </c>
       <c r="I29" t="s">
-        <v>843</v>
-      </c>
-      <c r="J29" t="s">
-        <v>817</v>
-      </c>
-      <c r="K29" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="D30" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="F30" t="s">
-        <v>654</v>
+        <v>821</v>
+      </c>
+      <c r="G30" t="s">
+        <v>266</v>
+      </c>
+      <c r="H30" t="s">
+        <v>822</v>
       </c>
       <c r="I30" t="s">
-        <v>250</v>
-      </c>
-      <c r="J30" t="s">
-        <v>816</v>
-      </c>
-      <c r="K30" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>452</v>
+        <v>383</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>453</v>
+        <v>384</v>
       </c>
       <c r="D31" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="F31" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="G31" t="s">
         <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="I31" t="s">
-        <v>825</v>
-      </c>
-      <c r="J31" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>439</v>
+      </c>
+      <c r="D32" t="s">
+        <v>426</v>
+      </c>
+      <c r="F32" t="s">
         <v>817</v>
-      </c>
-      <c r="K31" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-      <c r="C32" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" t="s">
-        <v>438</v>
-      </c>
-      <c r="F32" t="s">
-        <v>455</v>
       </c>
       <c r="G32" t="s">
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>456</v>
+        <v>818</v>
       </c>
       <c r="I32" t="s">
-        <v>457</v>
-      </c>
-      <c r="J32" t="s">
-        <v>816</v>
-      </c>
-      <c r="K32" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>458</v>
+        <v>366</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>459</v>
+        <v>367</v>
       </c>
       <c r="D33" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="F33" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="G33" t="s">
         <v>4</v>
       </c>
       <c r="H33" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="I33" t="s">
-        <v>827</v>
-      </c>
-      <c r="J33" t="s">
-        <v>817</v>
-      </c>
-      <c r="K33" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>426</v>
+      </c>
+      <c r="F34" t="s">
+        <v>642</v>
+      </c>
+      <c r="G34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>643</v>
+      </c>
+      <c r="I34" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B35">
         <v>1</v>
       </c>
-      <c r="C34" t="s">
-        <v>461</v>
-      </c>
-      <c r="D34" t="s">
-        <v>438</v>
-      </c>
-      <c r="F34" t="s">
-        <v>462</v>
-      </c>
-      <c r="G34" t="s">
-        <v>463</v>
-      </c>
-      <c r="H34" t="s">
-        <v>464</v>
-      </c>
-      <c r="I34" t="s">
-        <v>465</v>
-      </c>
-      <c r="J34" t="s">
-        <v>816</v>
-      </c>
-      <c r="K34" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
       <c r="C35" t="s">
-        <v>467</v>
+        <v>374</v>
       </c>
       <c r="D35" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="F35" t="s">
+        <v>842</v>
+      </c>
+      <c r="G35" t="s">
         <v>846</v>
       </c>
-      <c r="G35" t="s">
-        <v>4</v>
-      </c>
       <c r="H35" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
       <c r="I35" t="s">
-        <v>829</v>
-      </c>
-      <c r="J35" t="s">
-        <v>817</v>
-      </c>
-      <c r="K35" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>468</v>
+        <v>153</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>469</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>438</v>
+        <v>359</v>
       </c>
       <c r="F36" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G36" t="s">
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
       <c r="I36" t="s">
-        <v>831</v>
-      </c>
-      <c r="J36" t="s">
-        <v>817</v>
-      </c>
-      <c r="K36" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>439</v>
+        <v>380</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="D37" t="s">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="F37" t="s">
-        <v>441</v>
+        <v>851</v>
       </c>
       <c r="G37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>442</v>
+        <v>850</v>
       </c>
       <c r="I37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J37" t="s">
-        <v>816</v>
-      </c>
-      <c r="K37" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>444</v>
+        <v>155</v>
       </c>
       <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>364</v>
+      </c>
+      <c r="D38" t="s">
+        <v>354</v>
+      </c>
+      <c r="F38" t="s">
+        <v>853</v>
+      </c>
+      <c r="I38" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B39">
         <v>3</v>
       </c>
-      <c r="C38">
-        <v>470</v>
-      </c>
-      <c r="D38" t="s">
-        <v>438</v>
-      </c>
-      <c r="F38" t="s">
-        <v>618</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="C39" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" t="s">
+        <v>854</v>
+      </c>
+      <c r="F39" s="47" t="s">
         <v>620</v>
       </c>
-      <c r="H38" t="s">
-        <v>619</v>
-      </c>
-      <c r="I38" t="s">
-        <v>852</v>
-      </c>
-      <c r="J38" t="s">
-        <v>817</v>
-      </c>
-      <c r="K38" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="B39">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" t="s">
-        <v>438</v>
-      </c>
-      <c r="F39" t="s">
-        <v>446</v>
-      </c>
-      <c r="G39" t="s">
-        <v>447</v>
-      </c>
-      <c r="H39" t="s">
-        <v>448</v>
-      </c>
-      <c r="I39" t="s">
-        <v>449</v>
-      </c>
-      <c r="J39" t="s">
-        <v>816</v>
-      </c>
-      <c r="K39" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G39" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>621</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>451</v>
+        <v>397</v>
       </c>
       <c r="D40" t="s">
-        <v>438</v>
-      </c>
-      <c r="F40" t="s">
-        <v>832</v>
-      </c>
-      <c r="G40" t="s">
-        <v>4</v>
-      </c>
-      <c r="H40" t="s">
-        <v>833</v>
+        <v>398</v>
+      </c>
+      <c r="E40" t="s">
+        <v>399</v>
       </c>
       <c r="I40" t="s">
-        <v>834</v>
-      </c>
-      <c r="J40" t="s">
-        <v>817</v>
-      </c>
-      <c r="K40" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>471</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
-        <v>472</v>
+        <v>403</v>
       </c>
       <c r="I41" t="s">
-        <v>473</v>
-      </c>
-      <c r="J41" t="s">
-        <v>817</v>
-      </c>
-      <c r="K41" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>255</v>
+        <v>405</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>406</v>
       </c>
       <c r="D42" t="s">
-        <v>474</v>
-      </c>
-      <c r="E42" t="s">
-        <v>475</v>
-      </c>
-      <c r="F42" t="s">
-        <v>686</v>
+        <v>407</v>
       </c>
       <c r="I42" t="s">
-        <v>476</v>
-      </c>
-      <c r="J42" t="s">
-        <v>816</v>
-      </c>
-      <c r="K42" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="D43" t="s">
-        <v>478</v>
-      </c>
-      <c r="E43" t="s">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="F43" t="s">
-        <v>644</v>
+        <v>857</v>
+      </c>
+      <c r="G43" t="s">
+        <v>846</v>
+      </c>
+      <c r="H43" t="s">
+        <v>855</v>
       </c>
       <c r="I43" t="s">
-        <v>480</v>
-      </c>
-      <c r="J43" t="s">
-        <v>816</v>
-      </c>
-      <c r="K43" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>260</v>
+        <v>415</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
-      </c>
-      <c r="D44" t="s">
-        <v>481</v>
-      </c>
-      <c r="E44" t="s">
-        <v>482</v>
+        <v>416</v>
+      </c>
+      <c r="D44">
+        <v>402</v>
       </c>
       <c r="F44" t="s">
-        <v>310</v>
+        <v>861</v>
       </c>
       <c r="G44" t="s">
-        <v>31</v>
+        <v>858</v>
       </c>
       <c r="H44" t="s">
-        <v>262</v>
+        <v>859</v>
       </c>
       <c r="I44" t="s">
-        <v>483</v>
-      </c>
-      <c r="J44" t="s">
-        <v>816</v>
-      </c>
-      <c r="K44" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>263</v>
+        <v>417</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>331</v>
-      </c>
-      <c r="D45" t="s">
-        <v>481</v>
-      </c>
-      <c r="E45" t="s">
-        <v>484</v>
+        <v>79</v>
+      </c>
+      <c r="D45">
+        <v>603</v>
       </c>
       <c r="F45" t="s">
-        <v>312</v>
+        <v>864</v>
       </c>
       <c r="G45" t="s">
-        <v>259</v>
+        <v>865</v>
       </c>
       <c r="H45" t="s">
-        <v>265</v>
+        <v>862</v>
       </c>
       <c r="I45" t="s">
-        <v>835</v>
-      </c>
-      <c r="J45" t="s">
-        <v>817</v>
-      </c>
-      <c r="K45" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="D46" t="s">
-        <v>487</v>
-      </c>
-      <c r="F46" t="s">
-        <v>836</v>
-      </c>
-      <c r="G46" t="s">
-        <v>267</v>
-      </c>
-      <c r="H46" t="s">
-        <v>837</v>
+        <v>460</v>
       </c>
       <c r="I46" t="s">
-        <v>838</v>
-      </c>
-      <c r="J46" t="s">
-        <v>817</v>
-      </c>
-      <c r="K46" t="s">
-        <v>902</v>
-      </c>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+    </row>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{CB182CE8-6328-574F-84CA-162C8ACED3C7}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I46">
-      <sortCondition ref="A1:A46"/>
+      <sortCondition descending="1" ref="F1:F46"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12317,2157 +12024,2157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="47" t="s">
+        <v>476</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>477</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>480</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>481</v>
+      </c>
+      <c r="J1" s="47" t="s">
+        <v>482</v>
+      </c>
+      <c r="K1" s="47" t="s">
+        <v>483</v>
+      </c>
+      <c r="L1" s="47" t="s">
+        <v>484</v>
+      </c>
+      <c r="M1" s="47" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="47" t="s">
+        <v>486</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>487</v>
+      </c>
+      <c r="C2" s="47" t="s">
         <v>488</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="D2" s="47"/>
+      <c r="E2" s="47" t="s">
         <v>489</v>
       </c>
-      <c r="C1" s="57" t="s">
-        <v>243</v>
-      </c>
-      <c r="D1" s="57" t="s">
+      <c r="F2" s="47" t="s">
         <v>490</v>
       </c>
-      <c r="E1" s="57" t="s">
-        <v>241</v>
-      </c>
-      <c r="F1" s="57" t="s">
-        <v>237</v>
-      </c>
-      <c r="G1" s="57" t="s">
+      <c r="G2" s="47" t="s">
         <v>491</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H2" s="47">
+        <v>5</v>
+      </c>
+      <c r="I2" s="47" t="s">
         <v>492</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="J2" s="47" t="s">
         <v>493</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="47" t="s">
         <v>494</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="B3" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="C3" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47">
+        <v>805</v>
+      </c>
+      <c r="F3" s="47" t="s">
         <v>496</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="G3" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H3" s="47">
+        <v>100</v>
+      </c>
+      <c r="I3" s="47" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="J3" s="47" t="s">
         <v>498</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="47" t="s">
         <v>499</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="B4" s="47" t="s">
         <v>500</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57" t="s">
+      <c r="C4" s="47" t="s">
         <v>501</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47">
+        <v>603</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>502</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G4" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H4" s="47">
+        <v>100</v>
+      </c>
+      <c r="I4" s="47" t="s">
         <v>503</v>
       </c>
-      <c r="H2" s="57">
+      <c r="J4" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="47" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>507</v>
+      </c>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H5" s="47">
         <v>5</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>504</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>505</v>
-      </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="57" t="s">
-        <v>506</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>507</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>463</v>
-      </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57">
+      <c r="I5" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="J5" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>514</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>516</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H6" s="47">
+        <v>100</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>518</v>
+      </c>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="47" t="s">
+        <v>519</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>520</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>521</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>522</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H7" s="47">
+        <v>10</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>523</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>524</v>
+      </c>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>526</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>527</v>
+      </c>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47">
         <v>805</v>
       </c>
-      <c r="F3" s="57" t="s">
+      <c r="F8" s="47" t="s">
+        <v>528</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H8" s="47">
+        <v>50</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>529</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="47" t="s">
+        <v>531</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>533</v>
+      </c>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>534</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H9" s="47">
+        <v>50</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>535</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>536</v>
+      </c>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>538</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>539</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47" t="s">
+        <v>540</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>541</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H10" s="47">
+        <v>5</v>
+      </c>
+      <c r="I10" s="47" t="s">
+        <v>542</v>
+      </c>
+      <c r="J10" s="47" t="s">
+        <v>543</v>
+      </c>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="47" t="s">
+        <v>544</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>545</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47">
+        <v>805</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>547</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H11" s="47">
+        <v>20</v>
+      </c>
+      <c r="I11" s="47" t="s">
+        <v>548</v>
+      </c>
+      <c r="J11" s="47" t="s">
+        <v>549</v>
+      </c>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="47" t="s">
+        <v>550</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>551</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47">
+        <v>603</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>552</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H12" s="47">
+        <v>100</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>553</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>554</v>
+      </c>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47">
+        <v>402</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>557</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H13" s="47">
+        <v>100</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>558</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="47" t="s">
+        <v>560</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>561</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>539</v>
+      </c>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47" t="s">
+        <v>562</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>563</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H14" s="47">
+        <v>5</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>564</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>565</v>
+      </c>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="47" t="s">
+        <v>566</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>567</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47">
+        <v>805</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>568</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H15" s="47">
+        <v>100</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>569</v>
+      </c>
+      <c r="J15" s="47" t="s">
+        <v>570</v>
+      </c>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
+        <v>571</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>572</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47" t="s">
+        <v>573</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>574</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H16" s="47">
+        <v>5</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>575</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>576</v>
+      </c>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="47" t="s">
+        <v>577</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>578</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>579</v>
+      </c>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47" t="s">
+        <v>580</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>581</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H17" s="47">
+        <v>10</v>
+      </c>
+      <c r="I17" s="48">
+        <v>30864</v>
+      </c>
+      <c r="J17" s="47" t="s">
+        <v>582</v>
+      </c>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="47" t="s">
+        <v>583</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>584</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>585</v>
+      </c>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47" t="s">
+        <v>586</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>587</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H18" s="47">
+        <v>5</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>588</v>
+      </c>
+      <c r="J18" s="47" t="s">
+        <v>589</v>
+      </c>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="47" t="s">
+        <v>590</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>591</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>592</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47" t="s">
+        <v>593</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>594</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H19" s="47">
+        <v>10</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>595</v>
+      </c>
+      <c r="J19" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="47" t="s">
+        <v>596</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>597</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>598</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47">
+        <v>603</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>599</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H20" s="47">
+        <v>60</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>600</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>601</v>
+      </c>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47" t="s">
+        <v>602</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>603</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H21" s="47">
+        <v>200</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>604</v>
+      </c>
+      <c r="J21" s="47" t="s">
+        <v>605</v>
+      </c>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="47" t="s">
+        <v>606</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>607</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47">
+        <v>603</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>609</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H22" s="47">
+        <v>100</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>610</v>
+      </c>
+      <c r="J22" s="47" t="s">
+        <v>611</v>
+      </c>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="47" t="s">
+        <v>612</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>613</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47">
+        <v>603</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>614</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H23" s="47">
+        <v>100</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="J23" s="47" t="s">
+        <v>498</v>
+      </c>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>616</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>521</v>
+      </c>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>617</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H24" s="47">
+        <v>20</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>618</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>619</v>
+      </c>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="47" t="s">
+        <v>620</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>621</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47">
+        <v>402</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>622</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H25" s="47">
+        <v>100</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="J25" s="47" t="s">
+        <v>518</v>
+      </c>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="47" t="s">
+        <v>623</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>624</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47">
+        <v>603</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>625</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H26" s="47">
+        <v>100</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>627</v>
+      </c>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>629</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>546</v>
+      </c>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47">
+        <v>603</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H27" s="47">
+        <v>40</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="J27" s="47" t="s">
+        <v>518</v>
+      </c>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="47" t="s">
+        <v>632</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>633</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>579</v>
+      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H28" s="47">
+        <v>10</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>635</v>
+      </c>
+      <c r="J28" s="47" t="s">
+        <v>636</v>
+      </c>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="47" t="s">
+        <v>637</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>377</v>
+      </c>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47">
+        <v>402</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>639</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H29" s="47">
+        <v>100</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="J29" s="47" t="s">
+        <v>641</v>
+      </c>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="47" t="s">
+        <v>642</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>643</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47">
+        <v>402</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>644</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H30" s="47">
+        <v>100</v>
+      </c>
+      <c r="I30" s="47" t="s">
+        <v>645</v>
+      </c>
+      <c r="J30" s="47" t="s">
+        <v>646</v>
+      </c>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="47" t="s">
+        <v>647</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>648</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47">
+        <v>402</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H31" s="47">
+        <v>100</v>
+      </c>
+      <c r="I31" s="47" t="s">
+        <v>650</v>
+      </c>
+      <c r="J31" s="47" t="s">
+        <v>651</v>
+      </c>
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>357</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47">
+        <v>402</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>652</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H32" s="47">
+        <v>100</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>653</v>
+      </c>
+      <c r="J32" s="47" t="s">
+        <v>654</v>
+      </c>
+      <c r="K32" s="47"/>
+      <c r="L32" s="47"/>
+      <c r="M32" s="47"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47" t="s">
+        <v>655</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>656</v>
+      </c>
+      <c r="G33" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H33" s="47">
+        <v>10</v>
+      </c>
+      <c r="I33" s="47" t="s">
+        <v>657</v>
+      </c>
+      <c r="J33" s="47" t="s">
+        <v>658</v>
+      </c>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="47"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>659</v>
+      </c>
+      <c r="G34" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H34" s="47">
+        <v>10</v>
+      </c>
+      <c r="I34" s="47" t="s">
+        <v>660</v>
+      </c>
+      <c r="J34" s="47" t="s">
+        <v>661</v>
+      </c>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47">
+        <v>402</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>662</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H35" s="47">
+        <v>100</v>
+      </c>
+      <c r="I35" s="47" t="s">
+        <v>645</v>
+      </c>
+      <c r="J35" s="47" t="s">
+        <v>646</v>
+      </c>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="47" t="s">
+        <v>663</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>664</v>
+      </c>
+      <c r="C36" s="47" t="s">
+        <v>377</v>
+      </c>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47">
+        <v>603</v>
+      </c>
+      <c r="F36" s="47" t="s">
+        <v>665</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H36" s="47">
+        <v>100</v>
+      </c>
+      <c r="I36" s="47" t="s">
+        <v>666</v>
+      </c>
+      <c r="J36" s="47" t="s">
+        <v>667</v>
+      </c>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="47" t="s">
+        <v>668</v>
+      </c>
+      <c r="B37" s="47" t="s">
+        <v>669</v>
+      </c>
+      <c r="C37" s="47" t="s">
+        <v>670</v>
+      </c>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47">
+        <v>402</v>
+      </c>
+      <c r="F37" s="47" t="s">
+        <v>671</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H37" s="47">
+        <v>100</v>
+      </c>
+      <c r="I37" s="47" t="s">
+        <v>672</v>
+      </c>
+      <c r="J37" s="47" t="s">
+        <v>673</v>
+      </c>
+      <c r="K37" s="47"/>
+      <c r="L37" s="47"/>
+      <c r="M37" s="47"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="47" t="s">
+        <v>674</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>675</v>
+      </c>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="47" t="s">
+        <v>676</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H38" s="47">
+        <v>10</v>
+      </c>
+      <c r="I38" s="47" t="s">
+        <v>677</v>
+      </c>
+      <c r="J38" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="47" t="s">
+        <v>679</v>
+      </c>
+      <c r="B39" s="47" t="s">
+        <v>680</v>
+      </c>
+      <c r="C39" s="47" t="s">
+        <v>681</v>
+      </c>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47" t="s">
+        <v>682</v>
+      </c>
+      <c r="F39" s="47" t="s">
+        <v>683</v>
+      </c>
+      <c r="G39" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H39" s="47">
+        <v>5</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>684</v>
+      </c>
+      <c r="J39" s="47" t="s">
+        <v>685</v>
+      </c>
+      <c r="K39" s="47"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="47" t="s">
+        <v>686</v>
+      </c>
+      <c r="B40" s="47" t="s">
+        <v>687</v>
+      </c>
+      <c r="C40" s="47" t="s">
+        <v>688</v>
+      </c>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47" t="s">
+        <v>689</v>
+      </c>
+      <c r="F40" s="47" t="s">
+        <v>690</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H40" s="47">
+        <v>10</v>
+      </c>
+      <c r="I40" s="47" t="s">
+        <v>691</v>
+      </c>
+      <c r="J40" s="47" t="s">
+        <v>692</v>
+      </c>
+      <c r="K40" s="47"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="47"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" s="47" t="s">
+        <v>693</v>
+      </c>
+      <c r="B41" s="47" t="s">
+        <v>694</v>
+      </c>
+      <c r="C41" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47" t="s">
+        <v>695</v>
+      </c>
+      <c r="F41" s="47" t="s">
+        <v>696</v>
+      </c>
+      <c r="G41" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H41" s="47">
+        <v>5</v>
+      </c>
+      <c r="I41" s="48">
+        <v>35962</v>
+      </c>
+      <c r="J41" s="47" t="s">
+        <v>697</v>
+      </c>
+      <c r="K41" s="47"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="47"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" s="47" t="s">
+        <v>351</v>
+      </c>
+      <c r="B42" s="47" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" s="47" t="s">
+        <v>352</v>
+      </c>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47">
+        <v>1206</v>
+      </c>
+      <c r="F42" s="47" t="s">
+        <v>698</v>
+      </c>
+      <c r="G42" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H42" s="47">
+        <v>10</v>
+      </c>
+      <c r="I42" s="47" t="s">
+        <v>699</v>
+      </c>
+      <c r="J42" s="47" t="s">
+        <v>549</v>
+      </c>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="B43" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47" t="s">
+        <v>602</v>
+      </c>
+      <c r="F43" s="47" t="s">
+        <v>603</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H43" s="47">
+        <v>40</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="J43" s="47" t="s">
+        <v>701</v>
+      </c>
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
+      <c r="M43" s="47"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="47" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>378</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>435</v>
+      </c>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47">
+        <v>402</v>
+      </c>
+      <c r="F44" s="47" t="s">
+        <v>702</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H44" s="47">
+        <v>30</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>703</v>
+      </c>
+      <c r="J44" s="47" t="s">
+        <v>704</v>
+      </c>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="47"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="47" t="s">
+        <v>705</v>
+      </c>
+      <c r="B45" s="47" t="s">
+        <v>706</v>
+      </c>
+      <c r="C45" s="47" t="s">
+        <v>707</v>
+      </c>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45" s="47">
+        <v>50</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>708</v>
+      </c>
+      <c r="J45" s="47" t="s">
+        <v>709</v>
+      </c>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" s="47" t="s">
+        <v>429</v>
+      </c>
+      <c r="B46" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="C46" s="47" t="s">
+        <v>710</v>
+      </c>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47">
+        <v>402</v>
+      </c>
+      <c r="F46" s="47" t="s">
+        <v>711</v>
+      </c>
+      <c r="G46" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H46" s="47">
+        <v>100</v>
+      </c>
+      <c r="I46" s="47" t="s">
+        <v>712</v>
+      </c>
+      <c r="J46" s="47" t="s">
+        <v>713</v>
+      </c>
+      <c r="K46" s="47"/>
+      <c r="L46" s="47"/>
+      <c r="M46" s="47"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="B47" s="47" t="s">
+        <v>345</v>
+      </c>
+      <c r="C47" s="47" t="s">
+        <v>710</v>
+      </c>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47" t="s">
+        <v>714</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>715</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H47" s="47">
+        <v>20</v>
+      </c>
+      <c r="I47" s="47" t="s">
+        <v>716</v>
+      </c>
+      <c r="J47" s="47" t="s">
+        <v>717</v>
+      </c>
+      <c r="K47" s="47"/>
+      <c r="L47" s="47"/>
+      <c r="M47" s="47"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" s="47" t="s">
+        <v>443</v>
+      </c>
+      <c r="B48" s="47" t="s">
+        <v>444</v>
+      </c>
+      <c r="C48" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47">
+        <v>402</v>
+      </c>
+      <c r="F48" s="47" t="s">
+        <v>718</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H48" s="47">
+        <v>20</v>
+      </c>
+      <c r="I48" s="47" t="s">
+        <v>719</v>
+      </c>
+      <c r="J48" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A49" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="B49" s="47" t="s">
+        <v>371</v>
+      </c>
+      <c r="C49" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47">
+        <v>402</v>
+      </c>
+      <c r="F49" s="47" t="s">
+        <v>721</v>
+      </c>
+      <c r="G49" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H49" s="47">
+        <v>100</v>
+      </c>
+      <c r="I49" s="47" t="s">
+        <v>722</v>
+      </c>
+      <c r="J49" s="47" t="s">
+        <v>723</v>
+      </c>
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="47"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="47" t="s">
+        <v>724</v>
+      </c>
+      <c r="B50" s="47" t="s">
+        <v>725</v>
+      </c>
+      <c r="C50" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47" t="s">
+        <v>726</v>
+      </c>
+      <c r="F50" s="47" t="s">
+        <v>727</v>
+      </c>
+      <c r="G50" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H50" s="47">
+        <v>5</v>
+      </c>
+      <c r="I50" s="47" t="s">
+        <v>728</v>
+      </c>
+      <c r="J50" s="47" t="s">
+        <v>729</v>
+      </c>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" s="47" t="s">
+        <v>730</v>
+      </c>
+      <c r="B51" s="47" t="s">
+        <v>731</v>
+      </c>
+      <c r="C51" s="47" t="s">
+        <v>675</v>
+      </c>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47" t="s">
+        <v>732</v>
+      </c>
+      <c r="F51" s="47" t="s">
+        <v>733</v>
+      </c>
+      <c r="G51" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H51" s="47">
+        <v>10</v>
+      </c>
+      <c r="I51" s="47" t="s">
+        <v>734</v>
+      </c>
+      <c r="J51" s="47" t="s">
+        <v>735</v>
+      </c>
+      <c r="K51" s="47"/>
+      <c r="L51" s="47"/>
+      <c r="M51" s="47"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="47" t="s">
+        <v>736</v>
+      </c>
+      <c r="B52" s="47" t="s">
+        <v>737</v>
+      </c>
+      <c r="C52" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47" t="s">
+        <v>738</v>
+      </c>
+      <c r="F52" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="G52" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H52" s="47">
+        <v>5</v>
+      </c>
+      <c r="I52" s="47" t="s">
+        <v>740</v>
+      </c>
+      <c r="J52" s="47" t="s">
+        <v>741</v>
+      </c>
+      <c r="K52" s="47"/>
+      <c r="L52" s="47"/>
+      <c r="M52" s="47"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" s="47" t="s">
+        <v>742</v>
+      </c>
+      <c r="B53" s="47" t="s">
+        <v>743</v>
+      </c>
+      <c r="C53" s="47" t="s">
+        <v>744</v>
+      </c>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47" t="s">
+        <v>745</v>
+      </c>
+      <c r="F53" s="47" t="s">
+        <v>746</v>
+      </c>
+      <c r="G53" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H53" s="47">
+        <v>5</v>
+      </c>
+      <c r="I53" s="47" t="s">
+        <v>747</v>
+      </c>
+      <c r="J53" s="47" t="s">
+        <v>748</v>
+      </c>
+      <c r="K53" s="47"/>
+      <c r="L53" s="47"/>
+      <c r="M53" s="47"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" s="47" t="s">
+        <v>749</v>
+      </c>
+      <c r="B54" s="47" t="s">
+        <v>750</v>
+      </c>
+      <c r="C54" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47">
+        <v>805</v>
+      </c>
+      <c r="F54" s="47" t="s">
+        <v>751</v>
+      </c>
+      <c r="G54" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H54" s="47">
+        <v>50</v>
+      </c>
+      <c r="I54" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="J54" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="K54" s="47"/>
+      <c r="L54" s="47"/>
+      <c r="M54" s="47"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="47" t="s">
+        <v>753</v>
+      </c>
+      <c r="B55" s="47" t="s">
+        <v>754</v>
+      </c>
+      <c r="C55" s="47" t="s">
+        <v>352</v>
+      </c>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47" t="s">
         <v>508</v>
       </c>
-      <c r="G3" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H3" s="57">
-        <v>100</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>509</v>
-      </c>
-      <c r="J3" s="57" t="s">
-        <v>510</v>
-      </c>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
-        <v>511</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>512</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>513</v>
-      </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57">
+      <c r="F55" s="47" t="s">
+        <v>755</v>
+      </c>
+      <c r="G55" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H55" s="47">
+        <v>5</v>
+      </c>
+      <c r="I55" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="J55" s="47" t="s">
+        <v>757</v>
+      </c>
+      <c r="K55" s="47"/>
+      <c r="L55" s="47"/>
+      <c r="M55" s="47"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" s="47" t="s">
+        <v>758</v>
+      </c>
+      <c r="B56" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="C56" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47" t="s">
+        <v>760</v>
+      </c>
+      <c r="F56" s="47" t="s">
+        <v>761</v>
+      </c>
+      <c r="G56" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H56" s="47">
+        <v>5</v>
+      </c>
+      <c r="I56" s="48">
+        <v>10388</v>
+      </c>
+      <c r="J56" s="47" t="s">
+        <v>762</v>
+      </c>
+      <c r="K56" s="47"/>
+      <c r="L56" s="47"/>
+      <c r="M56" s="47"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="47" t="s">
+        <v>763</v>
+      </c>
+      <c r="B57" s="47" t="s">
+        <v>764</v>
+      </c>
+      <c r="C57" s="47" t="s">
+        <v>765</v>
+      </c>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47" t="s">
+        <v>766</v>
+      </c>
+      <c r="F57" s="47" t="s">
+        <v>767</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H57" s="47">
+        <v>5</v>
+      </c>
+      <c r="I57" s="47" t="s">
+        <v>768</v>
+      </c>
+      <c r="J57" s="47" t="s">
+        <v>769</v>
+      </c>
+      <c r="K57" s="47"/>
+      <c r="L57" s="47"/>
+      <c r="M57" s="47"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="47" t="s">
+        <v>770</v>
+      </c>
+      <c r="B58" s="47" t="s">
+        <v>771</v>
+      </c>
+      <c r="C58" s="47" t="s">
+        <v>765</v>
+      </c>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47" t="s">
+        <v>766</v>
+      </c>
+      <c r="F58" s="47" t="s">
+        <v>767</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H58" s="47">
+        <v>20</v>
+      </c>
+      <c r="I58" s="47" t="s">
+        <v>772</v>
+      </c>
+      <c r="J58" s="47" t="s">
+        <v>773</v>
+      </c>
+      <c r="K58" s="47"/>
+      <c r="L58" s="47"/>
+      <c r="M58" s="47"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="B59" s="47" t="s">
+        <v>345</v>
+      </c>
+      <c r="C59" s="47" t="s">
+        <v>710</v>
+      </c>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47" t="s">
+        <v>714</v>
+      </c>
+      <c r="F59" s="47" t="s">
+        <v>715</v>
+      </c>
+      <c r="G59" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H59" s="47">
+        <v>30</v>
+      </c>
+      <c r="I59" s="47" t="s">
+        <v>774</v>
+      </c>
+      <c r="J59" s="47" t="s">
+        <v>775</v>
+      </c>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
+      <c r="M59" s="47"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="47" t="s">
+        <v>674</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="47" t="s">
+        <v>675</v>
+      </c>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="47" t="s">
+        <v>676</v>
+      </c>
+      <c r="G60" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H60" s="47">
+        <v>10</v>
+      </c>
+      <c r="I60" s="47" t="s">
+        <v>776</v>
+      </c>
+      <c r="J60" s="47" t="s">
+        <v>777</v>
+      </c>
+      <c r="K60" s="47"/>
+      <c r="L60" s="47"/>
+      <c r="M60" s="47"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="47" t="s">
+        <v>778</v>
+      </c>
+      <c r="B61" s="47" t="s">
+        <v>779</v>
+      </c>
+      <c r="C61" s="47" t="s">
+        <v>780</v>
+      </c>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="47" t="s">
+        <v>781</v>
+      </c>
+      <c r="G61" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H61" s="47">
+        <v>3</v>
+      </c>
+      <c r="I61" s="47" t="s">
+        <v>782</v>
+      </c>
+      <c r="J61" s="47" t="s">
+        <v>783</v>
+      </c>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
+      <c r="M61" s="47"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" s="47" t="s">
+        <v>784</v>
+      </c>
+      <c r="B62" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="C62" s="47" t="s">
+        <v>786</v>
+      </c>
+      <c r="D62" s="47"/>
+      <c r="E62" s="47" t="s">
+        <v>787</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>788</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H62" s="47">
+        <v>5</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>789</v>
+      </c>
+      <c r="J62" s="47" t="s">
+        <v>790</v>
+      </c>
+      <c r="K62" s="47"/>
+      <c r="L62" s="47"/>
+      <c r="M62" s="47"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="47" t="s">
+        <v>791</v>
+      </c>
+      <c r="B63" s="47" t="s">
+        <v>792</v>
+      </c>
+      <c r="C63" s="47" t="s">
+        <v>793</v>
+      </c>
+      <c r="D63" s="47"/>
+      <c r="E63" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="47" t="s">
+        <v>794</v>
+      </c>
+      <c r="G63" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H63" s="47">
+        <v>10</v>
+      </c>
+      <c r="I63" s="47" t="s">
+        <v>795</v>
+      </c>
+      <c r="J63" s="47" t="s">
+        <v>661</v>
+      </c>
+      <c r="K63" s="47"/>
+      <c r="L63" s="47"/>
+      <c r="M63" s="47"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" s="47" t="s">
+        <v>796</v>
+      </c>
+      <c r="B64" s="47" t="s">
+        <v>797</v>
+      </c>
+      <c r="C64" s="47" t="s">
+        <v>793</v>
+      </c>
+      <c r="D64" s="47"/>
+      <c r="E64" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="47" t="s">
+        <v>798</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H64" s="47">
+        <v>20</v>
+      </c>
+      <c r="I64" s="47" t="s">
+        <v>799</v>
+      </c>
+      <c r="J64" s="47" t="s">
+        <v>800</v>
+      </c>
+      <c r="K64" s="47"/>
+      <c r="L64" s="47"/>
+      <c r="M64" s="47"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65" s="47"/>
+      <c r="E65" s="47" t="s">
+        <v>602</v>
+      </c>
+      <c r="F65" s="47" t="s">
         <v>603</v>
       </c>
-      <c r="F4" s="57" t="s">
-        <v>514</v>
-      </c>
-      <c r="G4" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H4" s="57">
-        <v>100</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>515</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>516</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
-        <v>517</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>518</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>519</v>
-      </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57" t="s">
-        <v>520</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>521</v>
-      </c>
-      <c r="G5" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H5" s="57">
-        <v>5</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>522</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>523</v>
-      </c>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="57" t="s">
-        <v>524</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>525</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>526</v>
-      </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57" t="s">
-        <v>527</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>528</v>
-      </c>
-      <c r="G6" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H6" s="57">
-        <v>100</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>529</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>530</v>
-      </c>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
-        <v>531</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>532</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>533</v>
-      </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57" t="s">
-        <v>520</v>
-      </c>
-      <c r="F7" s="57" t="s">
-        <v>534</v>
-      </c>
-      <c r="G7" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H7" s="57">
-        <v>10</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>535</v>
-      </c>
-      <c r="J7" s="57" t="s">
-        <v>536</v>
-      </c>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
-        <v>537</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>538</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>539</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57">
-        <v>805</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>540</v>
-      </c>
-      <c r="G8" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H8" s="57">
+      <c r="G65" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="H65" s="47">
         <v>50</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>541</v>
-      </c>
-      <c r="J8" s="57" t="s">
-        <v>542</v>
-      </c>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="57" t="s">
-        <v>543</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>544</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>545</v>
-      </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57" t="s">
-        <v>527</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>546</v>
-      </c>
-      <c r="G9" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H9" s="57">
-        <v>50</v>
-      </c>
-      <c r="I9" s="57" t="s">
-        <v>547</v>
-      </c>
-      <c r="J9" s="57" t="s">
-        <v>548</v>
-      </c>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
-        <v>549</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>550</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57" t="s">
-        <v>552</v>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>553</v>
-      </c>
-      <c r="G10" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H10" s="57">
-        <v>5</v>
-      </c>
-      <c r="I10" s="57" t="s">
-        <v>554</v>
-      </c>
-      <c r="J10" s="57" t="s">
-        <v>555</v>
-      </c>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="57" t="s">
-        <v>556</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>557</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>558</v>
-      </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57">
-        <v>805</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>559</v>
-      </c>
-      <c r="G11" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H11" s="57">
-        <v>20</v>
-      </c>
-      <c r="I11" s="57" t="s">
-        <v>560</v>
-      </c>
-      <c r="J11" s="57" t="s">
-        <v>561</v>
-      </c>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="57" t="s">
-        <v>562</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>563</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>447</v>
-      </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57">
-        <v>603</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>564</v>
-      </c>
-      <c r="G12" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H12" s="57">
-        <v>100</v>
-      </c>
-      <c r="I12" s="57" t="s">
-        <v>565</v>
-      </c>
-      <c r="J12" s="57" t="s">
-        <v>566</v>
-      </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="57" t="s">
-        <v>567</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>568</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>447</v>
-      </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57">
-        <v>402</v>
-      </c>
-      <c r="F13" s="57" t="s">
-        <v>569</v>
-      </c>
-      <c r="G13" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H13" s="57">
-        <v>100</v>
-      </c>
-      <c r="I13" s="57" t="s">
-        <v>570</v>
-      </c>
-      <c r="J13" s="57" t="s">
-        <v>571</v>
-      </c>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="57" t="s">
-        <v>572</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>573</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57" t="s">
-        <v>574</v>
-      </c>
-      <c r="F14" s="57" t="s">
-        <v>575</v>
-      </c>
-      <c r="G14" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H14" s="57">
-        <v>5</v>
-      </c>
-      <c r="I14" s="57" t="s">
-        <v>576</v>
-      </c>
-      <c r="J14" s="57" t="s">
-        <v>577</v>
-      </c>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="57" t="s">
-        <v>578</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>579</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>513</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57">
-        <v>805</v>
-      </c>
-      <c r="F15" s="57" t="s">
-        <v>580</v>
-      </c>
-      <c r="G15" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H15" s="57">
-        <v>100</v>
-      </c>
-      <c r="I15" s="57" t="s">
-        <v>581</v>
-      </c>
-      <c r="J15" s="57" t="s">
-        <v>582</v>
-      </c>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="57" t="s">
-        <v>583</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>584</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57" t="s">
-        <v>585</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>586</v>
-      </c>
-      <c r="G16" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H16" s="57">
-        <v>5</v>
-      </c>
-      <c r="I16" s="57" t="s">
-        <v>587</v>
-      </c>
-      <c r="J16" s="57" t="s">
-        <v>588</v>
-      </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="57"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="57" t="s">
-        <v>589</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>590</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57" t="s">
-        <v>592</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>593</v>
-      </c>
-      <c r="G17" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H17" s="57">
-        <v>10</v>
-      </c>
-      <c r="I17" s="58">
-        <v>30864</v>
-      </c>
-      <c r="J17" s="57" t="s">
-        <v>594</v>
-      </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="57" t="s">
-        <v>595</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>596</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>597</v>
-      </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57" t="s">
-        <v>598</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>599</v>
-      </c>
-      <c r="G18" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H18" s="57">
-        <v>5</v>
-      </c>
-      <c r="I18" s="57" t="s">
-        <v>600</v>
-      </c>
-      <c r="J18" s="57" t="s">
-        <v>601</v>
-      </c>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="57" t="s">
-        <v>602</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>603</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>604</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57" t="s">
-        <v>605</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>606</v>
-      </c>
-      <c r="G19" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H19" s="57">
-        <v>10</v>
-      </c>
-      <c r="I19" s="57" t="s">
-        <v>607</v>
-      </c>
-      <c r="J19" s="57" t="s">
-        <v>542</v>
-      </c>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="57" t="s">
-        <v>608</v>
-      </c>
-      <c r="B20" s="57" t="s">
-        <v>609</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>610</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57">
-        <v>603</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>611</v>
-      </c>
-      <c r="G20" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H20" s="57">
-        <v>60</v>
-      </c>
-      <c r="I20" s="57" t="s">
-        <v>612</v>
-      </c>
-      <c r="J20" s="57" t="s">
-        <v>613</v>
-      </c>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57" t="s">
-        <v>614</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>615</v>
-      </c>
-      <c r="G21" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H21" s="57">
-        <v>200</v>
-      </c>
-      <c r="I21" s="57" t="s">
-        <v>616</v>
-      </c>
-      <c r="J21" s="57" t="s">
-        <v>617</v>
-      </c>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="57" t="s">
-        <v>618</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>619</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>620</v>
-      </c>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57">
-        <v>603</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>621</v>
-      </c>
-      <c r="G22" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H22" s="57">
-        <v>100</v>
-      </c>
-      <c r="I22" s="57" t="s">
-        <v>622</v>
-      </c>
-      <c r="J22" s="57" t="s">
-        <v>623</v>
-      </c>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="57" t="s">
-        <v>624</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>625</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>620</v>
-      </c>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57">
-        <v>603</v>
-      </c>
-      <c r="F23" s="57" t="s">
-        <v>626</v>
-      </c>
-      <c r="G23" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H23" s="57">
-        <v>100</v>
-      </c>
-      <c r="I23" s="57" t="s">
-        <v>509</v>
-      </c>
-      <c r="J23" s="57" t="s">
-        <v>510</v>
-      </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="57" t="s">
-        <v>627</v>
-      </c>
-      <c r="B24" s="57" t="s">
-        <v>628</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>533</v>
-      </c>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="57" t="s">
-        <v>629</v>
-      </c>
-      <c r="G24" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H24" s="57">
-        <v>20</v>
-      </c>
-      <c r="I24" s="57" t="s">
-        <v>630</v>
-      </c>
-      <c r="J24" s="57" t="s">
-        <v>631</v>
-      </c>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="57"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>632</v>
-      </c>
-      <c r="B25" s="57" t="s">
-        <v>633</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57">
-        <v>402</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>634</v>
-      </c>
-      <c r="G25" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H25" s="57">
-        <v>100</v>
-      </c>
-      <c r="I25" s="57" t="s">
-        <v>529</v>
-      </c>
-      <c r="J25" s="57" t="s">
-        <v>530</v>
-      </c>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="57" t="s">
-        <v>635</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>636</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57">
-        <v>603</v>
-      </c>
-      <c r="F26" s="57" t="s">
-        <v>637</v>
-      </c>
-      <c r="G26" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H26" s="57">
-        <v>100</v>
-      </c>
-      <c r="I26" s="57" t="s">
-        <v>638</v>
-      </c>
-      <c r="J26" s="57" t="s">
-        <v>639</v>
-      </c>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="57" t="s">
-        <v>640</v>
-      </c>
-      <c r="B27" s="57" t="s">
-        <v>641</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>558</v>
-      </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57">
-        <v>603</v>
-      </c>
-      <c r="F27" s="57" t="s">
-        <v>642</v>
-      </c>
-      <c r="G27" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H27" s="57">
-        <v>40</v>
-      </c>
-      <c r="I27" s="57" t="s">
-        <v>643</v>
-      </c>
-      <c r="J27" s="57" t="s">
-        <v>530</v>
-      </c>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="57" t="s">
-        <v>644</v>
-      </c>
-      <c r="B28" s="57" t="s">
-        <v>645</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>591</v>
-      </c>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>646</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H28" s="57">
-        <v>10</v>
-      </c>
-      <c r="I28" s="57" t="s">
-        <v>647</v>
-      </c>
-      <c r="J28" s="57" t="s">
-        <v>648</v>
-      </c>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="57" t="s">
-        <v>649</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>650</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>379</v>
-      </c>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57">
-        <v>402</v>
-      </c>
-      <c r="F29" s="57" t="s">
-        <v>651</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H29" s="57">
-        <v>100</v>
-      </c>
-      <c r="I29" s="57" t="s">
-        <v>652</v>
-      </c>
-      <c r="J29" s="57" t="s">
-        <v>653</v>
-      </c>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="57" t="s">
-        <v>654</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>655</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57">
-        <v>402</v>
-      </c>
-      <c r="F30" s="57" t="s">
-        <v>656</v>
-      </c>
-      <c r="G30" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H30" s="57">
-        <v>100</v>
-      </c>
-      <c r="I30" s="57" t="s">
-        <v>657</v>
-      </c>
-      <c r="J30" s="57" t="s">
-        <v>658</v>
-      </c>
-      <c r="K30" s="57"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="57"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="57" t="s">
-        <v>659</v>
-      </c>
-      <c r="B31" s="57" t="s">
-        <v>660</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57">
-        <v>402</v>
-      </c>
-      <c r="F31" s="57" t="s">
-        <v>661</v>
-      </c>
-      <c r="G31" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H31" s="57">
-        <v>100</v>
-      </c>
-      <c r="I31" s="57" t="s">
-        <v>662</v>
-      </c>
-      <c r="J31" s="57" t="s">
-        <v>663</v>
-      </c>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
-        <v>356</v>
-      </c>
-      <c r="B32" s="57" t="s">
-        <v>358</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57">
-        <v>402</v>
-      </c>
-      <c r="F32" s="57" t="s">
-        <v>664</v>
-      </c>
-      <c r="G32" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H32" s="57">
-        <v>100</v>
-      </c>
-      <c r="I32" s="57" t="s">
-        <v>665</v>
-      </c>
-      <c r="J32" s="57" t="s">
-        <v>666</v>
-      </c>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="57"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B33" s="57" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="57" t="s">
-        <v>422</v>
-      </c>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57" t="s">
-        <v>667</v>
-      </c>
-      <c r="F33" s="57" t="s">
-        <v>668</v>
-      </c>
-      <c r="G33" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H33" s="57">
-        <v>10</v>
-      </c>
-      <c r="I33" s="57" t="s">
-        <v>669</v>
-      </c>
-      <c r="J33" s="57" t="s">
-        <v>670</v>
-      </c>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="57"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>671</v>
-      </c>
-      <c r="G34" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H34" s="57">
-        <v>10</v>
-      </c>
-      <c r="I34" s="57" t="s">
-        <v>672</v>
-      </c>
-      <c r="J34" s="57" t="s">
-        <v>673</v>
-      </c>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="57" t="s">
-        <v>446</v>
-      </c>
-      <c r="B35" s="57" t="s">
-        <v>448</v>
-      </c>
-      <c r="C35" s="57" t="s">
-        <v>447</v>
-      </c>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57">
-        <v>402</v>
-      </c>
-      <c r="F35" s="57" t="s">
-        <v>674</v>
-      </c>
-      <c r="G35" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H35" s="57">
-        <v>100</v>
-      </c>
-      <c r="I35" s="57" t="s">
-        <v>657</v>
-      </c>
-      <c r="J35" s="57" t="s">
-        <v>658</v>
-      </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" s="57" t="s">
-        <v>675</v>
-      </c>
-      <c r="B36" s="57" t="s">
-        <v>676</v>
-      </c>
-      <c r="C36" s="57" t="s">
-        <v>379</v>
-      </c>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57">
-        <v>603</v>
-      </c>
-      <c r="F36" s="57" t="s">
-        <v>677</v>
-      </c>
-      <c r="G36" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H36" s="57">
-        <v>100</v>
-      </c>
-      <c r="I36" s="57" t="s">
-        <v>678</v>
-      </c>
-      <c r="J36" s="57" t="s">
-        <v>679</v>
-      </c>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="57"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="57" t="s">
-        <v>680</v>
-      </c>
-      <c r="B37" s="57" t="s">
-        <v>681</v>
-      </c>
-      <c r="C37" s="57" t="s">
-        <v>682</v>
-      </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57">
-        <v>402</v>
-      </c>
-      <c r="F37" s="57" t="s">
-        <v>683</v>
-      </c>
-      <c r="G37" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H37" s="57">
-        <v>100</v>
-      </c>
-      <c r="I37" s="57" t="s">
-        <v>684</v>
-      </c>
-      <c r="J37" s="57" t="s">
-        <v>685</v>
-      </c>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" s="57" t="s">
-        <v>686</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="57" t="s">
-        <v>687</v>
-      </c>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="57" t="s">
-        <v>688</v>
-      </c>
-      <c r="G38" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H38" s="57">
-        <v>10</v>
-      </c>
-      <c r="I38" s="57" t="s">
-        <v>689</v>
-      </c>
-      <c r="J38" s="57" t="s">
-        <v>690</v>
-      </c>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39" s="57" t="s">
-        <v>691</v>
-      </c>
-      <c r="B39" s="57" t="s">
-        <v>692</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>693</v>
-      </c>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57" t="s">
-        <v>694</v>
-      </c>
-      <c r="F39" s="57" t="s">
-        <v>695</v>
-      </c>
-      <c r="G39" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H39" s="57">
-        <v>5</v>
-      </c>
-      <c r="I39" s="57" t="s">
-        <v>696</v>
-      </c>
-      <c r="J39" s="57" t="s">
-        <v>697</v>
-      </c>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" s="57" t="s">
-        <v>698</v>
-      </c>
-      <c r="B40" s="57" t="s">
-        <v>699</v>
-      </c>
-      <c r="C40" s="57" t="s">
-        <v>700</v>
-      </c>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57" t="s">
-        <v>701</v>
-      </c>
-      <c r="F40" s="57" t="s">
-        <v>702</v>
-      </c>
-      <c r="G40" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H40" s="57">
-        <v>10</v>
-      </c>
-      <c r="I40" s="57" t="s">
-        <v>703</v>
-      </c>
-      <c r="J40" s="57" t="s">
-        <v>704</v>
-      </c>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="57" t="s">
-        <v>705</v>
-      </c>
-      <c r="B41" s="57" t="s">
-        <v>706</v>
-      </c>
-      <c r="C41" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57" t="s">
-        <v>707</v>
-      </c>
-      <c r="F41" s="57" t="s">
-        <v>708</v>
-      </c>
-      <c r="G41" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H41" s="57">
-        <v>5</v>
-      </c>
-      <c r="I41" s="58">
-        <v>35962</v>
-      </c>
-      <c r="J41" s="57" t="s">
-        <v>709</v>
-      </c>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="57"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>349</v>
-      </c>
-      <c r="C42" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57">
-        <v>1206</v>
-      </c>
-      <c r="F42" s="57" t="s">
-        <v>710</v>
-      </c>
-      <c r="G42" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H42" s="57">
-        <v>10</v>
-      </c>
-      <c r="I42" s="57" t="s">
-        <v>711</v>
-      </c>
-      <c r="J42" s="57" t="s">
-        <v>561</v>
-      </c>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="B43" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57" t="s">
-        <v>614</v>
-      </c>
-      <c r="F43" s="57" t="s">
-        <v>615</v>
-      </c>
-      <c r="G43" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H43" s="57">
-        <v>40</v>
-      </c>
-      <c r="I43" s="57" t="s">
-        <v>712</v>
-      </c>
-      <c r="J43" s="57" t="s">
-        <v>713</v>
-      </c>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" s="57" t="s">
-        <v>378</v>
-      </c>
-      <c r="B44" s="57" t="s">
-        <v>380</v>
-      </c>
-      <c r="C44" s="57" t="s">
-        <v>447</v>
-      </c>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57">
-        <v>402</v>
-      </c>
-      <c r="F44" s="57" t="s">
-        <v>714</v>
-      </c>
-      <c r="G44" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H44" s="57">
-        <v>30</v>
-      </c>
-      <c r="I44" s="57" t="s">
-        <v>715</v>
-      </c>
-      <c r="J44" s="57" t="s">
-        <v>716</v>
-      </c>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="57" t="s">
-        <v>717</v>
-      </c>
-      <c r="B45" s="57" t="s">
-        <v>718</v>
-      </c>
-      <c r="C45" s="57" t="s">
-        <v>719</v>
-      </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="G45" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="H45" s="57">
-        <v>50</v>
-      </c>
-      <c r="I45" s="57" t="s">
-        <v>720</v>
-      </c>
-      <c r="J45" s="57" t="s">
-        <v>721</v>
-      </c>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" s="57" t="s">
-        <v>441</v>
-      </c>
-      <c r="B46" s="57" t="s">
-        <v>442</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>722</v>
-      </c>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57">
-        <v>402</v>
-      </c>
-      <c r="F46" s="57" t="s">
-        <v>723</v>
-      </c>
-      <c r="G46" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H46" s="57">
-        <v>100</v>
-      </c>
-      <c r="I46" s="57" t="s">
-        <v>724</v>
-      </c>
-      <c r="J46" s="57" t="s">
-        <v>725</v>
-      </c>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="B47" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>722</v>
-      </c>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57" t="s">
-        <v>726</v>
-      </c>
-      <c r="F47" s="57" t="s">
-        <v>727</v>
-      </c>
-      <c r="G47" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H47" s="57">
-        <v>20</v>
-      </c>
-      <c r="I47" s="57" t="s">
-        <v>728</v>
-      </c>
-      <c r="J47" s="57" t="s">
-        <v>729</v>
-      </c>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="57"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="57" t="s">
-        <v>455</v>
-      </c>
-      <c r="B48" s="57" t="s">
-        <v>456</v>
-      </c>
-      <c r="C48" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57">
-        <v>402</v>
-      </c>
-      <c r="F48" s="57" t="s">
-        <v>730</v>
-      </c>
-      <c r="G48" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H48" s="57">
-        <v>20</v>
-      </c>
-      <c r="I48" s="57" t="s">
-        <v>731</v>
-      </c>
-      <c r="J48" s="57" t="s">
-        <v>732</v>
-      </c>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" s="57" t="s">
-        <v>372</v>
-      </c>
-      <c r="B49" s="57" t="s">
-        <v>373</v>
-      </c>
-      <c r="C49" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57">
-        <v>402</v>
-      </c>
-      <c r="F49" s="57" t="s">
-        <v>733</v>
-      </c>
-      <c r="G49" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H49" s="57">
-        <v>100</v>
-      </c>
-      <c r="I49" s="57" t="s">
-        <v>734</v>
-      </c>
-      <c r="J49" s="57" t="s">
-        <v>735</v>
-      </c>
-      <c r="K49" s="57"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="57"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="57" t="s">
-        <v>736</v>
-      </c>
-      <c r="B50" s="57" t="s">
-        <v>737</v>
-      </c>
-      <c r="C50" s="57" t="s">
-        <v>357</v>
-      </c>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57" t="s">
-        <v>738</v>
-      </c>
-      <c r="F50" s="57" t="s">
-        <v>739</v>
-      </c>
-      <c r="G50" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H50" s="57">
-        <v>5</v>
-      </c>
-      <c r="I50" s="57" t="s">
-        <v>740</v>
-      </c>
-      <c r="J50" s="57" t="s">
-        <v>741</v>
-      </c>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="57"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="57" t="s">
-        <v>742</v>
-      </c>
-      <c r="B51" s="57" t="s">
-        <v>743</v>
-      </c>
-      <c r="C51" s="57" t="s">
-        <v>687</v>
-      </c>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57" t="s">
-        <v>744</v>
-      </c>
-      <c r="F51" s="57" t="s">
-        <v>745</v>
-      </c>
-      <c r="G51" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H51" s="57">
-        <v>10</v>
-      </c>
-      <c r="I51" s="57" t="s">
-        <v>746</v>
-      </c>
-      <c r="J51" s="57" t="s">
-        <v>747</v>
-      </c>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-      <c r="M51" s="57"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="57" t="s">
-        <v>748</v>
-      </c>
-      <c r="B52" s="57" t="s">
-        <v>749</v>
-      </c>
-      <c r="C52" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57" t="s">
-        <v>750</v>
-      </c>
-      <c r="F52" s="57" t="s">
-        <v>751</v>
-      </c>
-      <c r="G52" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H52" s="57">
-        <v>5</v>
-      </c>
-      <c r="I52" s="57" t="s">
-        <v>752</v>
-      </c>
-      <c r="J52" s="57" t="s">
-        <v>753</v>
-      </c>
-      <c r="K52" s="57"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="57"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="57" t="s">
-        <v>754</v>
-      </c>
-      <c r="B53" s="57" t="s">
-        <v>755</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>756</v>
-      </c>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57" t="s">
-        <v>757</v>
-      </c>
-      <c r="F53" s="57" t="s">
-        <v>758</v>
-      </c>
-      <c r="G53" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H53" s="57">
-        <v>5</v>
-      </c>
-      <c r="I53" s="57" t="s">
-        <v>759</v>
-      </c>
-      <c r="J53" s="57" t="s">
-        <v>760</v>
-      </c>
-      <c r="K53" s="57"/>
-      <c r="L53" s="57"/>
-      <c r="M53" s="57"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="57" t="s">
-        <v>761</v>
-      </c>
-      <c r="B54" s="57" t="s">
-        <v>762</v>
-      </c>
-      <c r="C54" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57">
-        <v>805</v>
-      </c>
-      <c r="F54" s="57" t="s">
-        <v>763</v>
-      </c>
-      <c r="G54" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H54" s="57">
-        <v>50</v>
-      </c>
-      <c r="I54" s="57" t="s">
-        <v>764</v>
-      </c>
-      <c r="J54" s="57" t="s">
-        <v>542</v>
-      </c>
-      <c r="K54" s="57"/>
-      <c r="L54" s="57"/>
-      <c r="M54" s="57"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="57" t="s">
-        <v>765</v>
-      </c>
-      <c r="B55" s="57" t="s">
-        <v>766</v>
-      </c>
-      <c r="C55" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57" t="s">
-        <v>520</v>
-      </c>
-      <c r="F55" s="57" t="s">
-        <v>767</v>
-      </c>
-      <c r="G55" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H55" s="57">
-        <v>5</v>
-      </c>
-      <c r="I55" s="57" t="s">
-        <v>768</v>
-      </c>
-      <c r="J55" s="57" t="s">
-        <v>769</v>
-      </c>
-      <c r="K55" s="57"/>
-      <c r="L55" s="57"/>
-      <c r="M55" s="57"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="57" t="s">
-        <v>770</v>
-      </c>
-      <c r="B56" s="57" t="s">
-        <v>771</v>
-      </c>
-      <c r="C56" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57" t="s">
-        <v>772</v>
-      </c>
-      <c r="F56" s="57" t="s">
-        <v>773</v>
-      </c>
-      <c r="G56" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H56" s="57">
-        <v>5</v>
-      </c>
-      <c r="I56" s="58">
-        <v>10388</v>
-      </c>
-      <c r="J56" s="57" t="s">
-        <v>774</v>
-      </c>
-      <c r="K56" s="57"/>
-      <c r="L56" s="57"/>
-      <c r="M56" s="57"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="57" t="s">
-        <v>775</v>
-      </c>
-      <c r="B57" s="57" t="s">
-        <v>776</v>
-      </c>
-      <c r="C57" s="57" t="s">
-        <v>777</v>
-      </c>
-      <c r="D57" s="57"/>
-      <c r="E57" s="57" t="s">
-        <v>778</v>
-      </c>
-      <c r="F57" s="57" t="s">
-        <v>779</v>
-      </c>
-      <c r="G57" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H57" s="57">
-        <v>5</v>
-      </c>
-      <c r="I57" s="57" t="s">
-        <v>780</v>
-      </c>
-      <c r="J57" s="57" t="s">
-        <v>781</v>
-      </c>
-      <c r="K57" s="57"/>
-      <c r="L57" s="57"/>
-      <c r="M57" s="57"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="57" t="s">
-        <v>782</v>
-      </c>
-      <c r="B58" s="57" t="s">
-        <v>783</v>
-      </c>
-      <c r="C58" s="57" t="s">
-        <v>777</v>
-      </c>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57" t="s">
-        <v>778</v>
-      </c>
-      <c r="F58" s="57" t="s">
-        <v>779</v>
-      </c>
-      <c r="G58" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H58" s="57">
-        <v>20</v>
-      </c>
-      <c r="I58" s="57" t="s">
-        <v>784</v>
-      </c>
-      <c r="J58" s="57" t="s">
-        <v>785</v>
-      </c>
-      <c r="K58" s="57"/>
-      <c r="L58" s="57"/>
-      <c r="M58" s="57"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="B59" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>722</v>
-      </c>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57" t="s">
-        <v>726</v>
-      </c>
-      <c r="F59" s="57" t="s">
-        <v>727</v>
-      </c>
-      <c r="G59" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H59" s="57">
-        <v>30</v>
-      </c>
-      <c r="I59" s="57" t="s">
-        <v>786</v>
-      </c>
-      <c r="J59" s="57" t="s">
-        <v>787</v>
-      </c>
-      <c r="K59" s="57"/>
-      <c r="L59" s="57"/>
-      <c r="M59" s="57"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="57" t="s">
-        <v>686</v>
-      </c>
-      <c r="B60" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="57" t="s">
-        <v>687</v>
-      </c>
-      <c r="D60" s="57"/>
-      <c r="E60" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F60" s="57" t="s">
-        <v>688</v>
-      </c>
-      <c r="G60" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H60" s="57">
-        <v>10</v>
-      </c>
-      <c r="I60" s="57" t="s">
-        <v>788</v>
-      </c>
-      <c r="J60" s="57" t="s">
-        <v>789</v>
-      </c>
-      <c r="K60" s="57"/>
-      <c r="L60" s="57"/>
-      <c r="M60" s="57"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61" s="57" t="s">
-        <v>790</v>
-      </c>
-      <c r="B61" s="57" t="s">
-        <v>791</v>
-      </c>
-      <c r="C61" s="57" t="s">
-        <v>792</v>
-      </c>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" s="57" t="s">
-        <v>793</v>
-      </c>
-      <c r="G61" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H61" s="57">
-        <v>3</v>
-      </c>
-      <c r="I61" s="57" t="s">
-        <v>794</v>
-      </c>
-      <c r="J61" s="57" t="s">
-        <v>795</v>
-      </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="57"/>
-      <c r="M61" s="57"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A62" s="57" t="s">
-        <v>796</v>
-      </c>
-      <c r="B62" s="57" t="s">
-        <v>797</v>
-      </c>
-      <c r="C62" s="57" t="s">
-        <v>798</v>
-      </c>
-      <c r="D62" s="57"/>
-      <c r="E62" s="57" t="s">
-        <v>799</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>800</v>
-      </c>
-      <c r="G62" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H62" s="57">
-        <v>5</v>
-      </c>
-      <c r="I62" s="57" t="s">
+      <c r="I65" s="47" t="s">
         <v>801</v>
       </c>
-      <c r="J62" s="57" t="s">
+      <c r="J65" s="47" t="s">
         <v>802</v>
       </c>
-      <c r="K62" s="57"/>
-      <c r="L62" s="57"/>
-      <c r="M62" s="57"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A63" s="57" t="s">
-        <v>803</v>
-      </c>
-      <c r="B63" s="57" t="s">
-        <v>804</v>
-      </c>
-      <c r="C63" s="57" t="s">
-        <v>805</v>
-      </c>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="F63" s="57" t="s">
-        <v>806</v>
-      </c>
-      <c r="G63" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H63" s="57">
-        <v>10</v>
-      </c>
-      <c r="I63" s="57" t="s">
-        <v>807</v>
-      </c>
-      <c r="J63" s="57" t="s">
-        <v>673</v>
-      </c>
-      <c r="K63" s="57"/>
-      <c r="L63" s="57"/>
-      <c r="M63" s="57"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A64" s="57" t="s">
-        <v>808</v>
-      </c>
-      <c r="B64" s="57" t="s">
-        <v>809</v>
-      </c>
-      <c r="C64" s="57" t="s">
-        <v>805</v>
-      </c>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="57" t="s">
-        <v>810</v>
-      </c>
-      <c r="G64" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H64" s="57">
-        <v>20</v>
-      </c>
-      <c r="I64" s="57" t="s">
-        <v>811</v>
-      </c>
-      <c r="J64" s="57" t="s">
-        <v>812</v>
-      </c>
-      <c r="K64" s="57"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A65" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="B65" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57" t="s">
-        <v>614</v>
-      </c>
-      <c r="F65" s="57" t="s">
-        <v>615</v>
-      </c>
-      <c r="G65" s="57" t="s">
-        <v>503</v>
-      </c>
-      <c r="H65" s="57">
-        <v>50</v>
-      </c>
-      <c r="I65" s="57" t="s">
-        <v>813</v>
-      </c>
-      <c r="J65" s="57" t="s">
-        <v>814</v>
-      </c>
-      <c r="K65" s="57"/>
-      <c r="L65" s="57"/>
-      <c r="M65" s="57"/>
+      <c r="K65" s="47"/>
+      <c r="L65" s="47"/>
+      <c r="M65" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hardware/BodyTempSens_Data.xlsx
+++ b/hardware/BodyTempSens_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daanheetkamp/Desktop/BodyTempSensor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daanheetkamp/Desktop/heart-heat-sensor/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFC80BE-FF6D-F947-A5FA-7AEC4A821F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A290EE3-9C77-A740-B64B-26226019A371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="68800" windowHeight="28200" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="4" r:id="rId1"/>
@@ -3363,16 +3363,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3384,14 +3378,20 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3402,7 +3402,207 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
           <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3466,6 +3666,158 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -3491,6 +3843,62 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3538,7 +3946,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3554,7 +3962,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3602,7 +4010,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3618,7 +4026,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3659,414 +4067,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4756,15 +4756,15 @@
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2212110099_20260617034224" connectionId="2" xr16:uid="{06E6BE92-5986-4143-9189-C64D0AAC269F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2407090249_20260617034145" connectionId="3" xr16:uid="{9F228B63-54CA-1A4A-9361-CAB5D71DFF0A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2407090249_20260617034145" connectionId="3" xr16:uid="{9F228B63-54CA-1A4A-9361-CAB5D71DFF0A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2509140097_20260617034302_1" connectionId="4" xr16:uid="{636388EF-35EB-4340-B01C-0AE102A00007}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2509140097_20260617034302_1" connectionId="4" xr16:uid="{636388EF-35EB-4340-B01C-0AE102A00007}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="LCSC__WM2212110099_20260617034224" connectionId="2" xr16:uid="{06E6BE92-5986-4143-9189-C64D0AAC269F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6988,30 +6988,30 @@
       <c r="F1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="N1" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="Y1" s="49" t="s">
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="Y1" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="58"/>
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+      <c r="AH1" s="58"/>
     </row>
     <row r="2" spans="1:47" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -7270,10 +7270,10 @@
       <c r="AH5" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="AJ5" s="56" t="s">
+      <c r="AJ5" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="AK5" s="57"/>
+      <c r="AK5" s="50"/>
       <c r="AM5" t="s">
         <v>233</v>
       </c>
@@ -7694,24 +7694,24 @@
         <f>Y13*AB13</f>
         <v>0.39599999999999996</v>
       </c>
-      <c r="AE13" s="53" t="s">
+      <c r="AE13" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="54"/>
-      <c r="AH13" s="54"/>
-      <c r="AI13" s="54"/>
-      <c r="AJ13" s="54"/>
-      <c r="AK13" s="55"/>
-      <c r="AO13" s="53" t="s">
+      <c r="AF13" s="52"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="52"/>
+      <c r="AK13" s="53"/>
+      <c r="AO13" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="AP13" s="54"/>
-      <c r="AQ13" s="54"/>
-      <c r="AR13" s="54"/>
-      <c r="AS13" s="54"/>
-      <c r="AT13" s="54"/>
-      <c r="AU13" s="55"/>
+      <c r="AP13" s="52"/>
+      <c r="AQ13" s="52"/>
+      <c r="AR13" s="52"/>
+      <c r="AS13" s="52"/>
+      <c r="AT13" s="52"/>
+      <c r="AU13" s="53"/>
     </row>
     <row r="14" spans="1:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="P14" s="4">
@@ -7732,28 +7732,28 @@
         <v>0.86</v>
       </c>
       <c r="AC14" s="4"/>
-      <c r="AE14" s="50" t="s">
+      <c r="AE14" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="AF14" s="51"/>
-      <c r="AG14" s="58"/>
+      <c r="AF14" s="55"/>
+      <c r="AG14" s="56"/>
       <c r="AH14" s="13"/>
-      <c r="AI14" s="50" t="s">
+      <c r="AI14" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="AJ14" s="51"/>
-      <c r="AK14" s="52"/>
-      <c r="AO14" s="50" t="s">
+      <c r="AJ14" s="55"/>
+      <c r="AK14" s="57"/>
+      <c r="AO14" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="AP14" s="51"/>
-      <c r="AQ14" s="58"/>
+      <c r="AP14" s="55"/>
+      <c r="AQ14" s="56"/>
       <c r="AR14" s="13"/>
-      <c r="AS14" s="50" t="s">
+      <c r="AS14" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="AT14" s="51"/>
-      <c r="AU14" s="52"/>
+      <c r="AT14" s="55"/>
+      <c r="AU14" s="57"/>
     </row>
     <row r="15" spans="1:47" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
@@ -7876,50 +7876,50 @@
         <f>J8-(J13/2)</f>
         <v>1.1308825454545455</v>
       </c>
-      <c r="AE19" s="53" t="s">
+      <c r="AE19" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="AF19" s="54"/>
-      <c r="AG19" s="54"/>
-      <c r="AH19" s="54"/>
-      <c r="AI19" s="54"/>
-      <c r="AJ19" s="54"/>
-      <c r="AK19" s="55"/>
-      <c r="AO19" s="53" t="s">
+      <c r="AF19" s="52"/>
+      <c r="AG19" s="52"/>
+      <c r="AH19" s="52"/>
+      <c r="AI19" s="52"/>
+      <c r="AJ19" s="52"/>
+      <c r="AK19" s="53"/>
+      <c r="AO19" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="AP19" s="54"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="54"/>
-      <c r="AS19" s="54"/>
-      <c r="AT19" s="54"/>
-      <c r="AU19" s="55"/>
+      <c r="AP19" s="52"/>
+      <c r="AQ19" s="52"/>
+      <c r="AR19" s="52"/>
+      <c r="AS19" s="52"/>
+      <c r="AT19" s="52"/>
+      <c r="AU19" s="53"/>
     </row>
     <row r="20" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="AE20" s="50" t="s">
+      <c r="AE20" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="AF20" s="51"/>
-      <c r="AG20" s="58"/>
+      <c r="AF20" s="55"/>
+      <c r="AG20" s="56"/>
       <c r="AH20" s="7"/>
-      <c r="AI20" s="50" t="s">
+      <c r="AI20" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="AJ20" s="51"/>
-      <c r="AK20" s="52"/>
-      <c r="AO20" s="50" t="s">
+      <c r="AJ20" s="55"/>
+      <c r="AK20" s="57"/>
+      <c r="AO20" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="AP20" s="51"/>
-      <c r="AQ20" s="58"/>
+      <c r="AP20" s="55"/>
+      <c r="AQ20" s="56"/>
       <c r="AR20" s="7"/>
-      <c r="AS20" s="50" t="s">
+      <c r="AS20" s="54" t="s">
         <v>212</v>
       </c>
-      <c r="AT20" s="51"/>
-      <c r="AU20" s="52"/>
+      <c r="AT20" s="55"/>
+      <c r="AU20" s="57"/>
     </row>
     <row r="21" spans="6:47" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AE21" s="31" t="s">
@@ -8018,10 +8018,10 @@
     <row r="23" spans="6:47" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="6:47" x14ac:dyDescent="0.2">
-      <c r="AE26" s="56" t="s">
+      <c r="AE26" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="AF26" s="57"/>
+      <c r="AF26" s="50"/>
     </row>
     <row r="27" spans="6:47" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AE27" s="28" t="s">
@@ -8079,13 +8079,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="16">
-    <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="AO13:AU13"/>
-    <mergeCell ref="AO14:AQ14"/>
-    <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AO19:AU19"/>
-    <mergeCell ref="AO20:AQ20"/>
-    <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="N1:W1"/>
     <mergeCell ref="Y1:AH1"/>
     <mergeCell ref="AI14:AK14"/>
@@ -8095,6 +8088,13 @@
     <mergeCell ref="AJ5:AK5"/>
     <mergeCell ref="AE20:AG20"/>
     <mergeCell ref="AE14:AG14"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AO13:AU13"/>
+    <mergeCell ref="AO14:AQ14"/>
+    <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AO19:AU19"/>
+    <mergeCell ref="AO20:AQ20"/>
+    <mergeCell ref="AS20:AU20"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="AE14">
@@ -8112,101 +8112,101 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE20">
-    <cfRule type="cellIs" dxfId="83" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="92" operator="equal">
+      <formula>"++"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="89" operator="equal">
       <formula>"--"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="90" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="91" operator="equal">
       <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="92" operator="equal">
-      <formula>"++"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE26:AF26">
-    <cfRule type="cellIs" dxfId="79" priority="41" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="79" priority="44" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="43" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="77" priority="42" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="43" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="44" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="76" priority="41" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE15:AG15">
-    <cfRule type="cellIs" dxfId="75" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="64" operator="equal">
+      <formula>"++"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="61" operator="equal">
       <formula>"--"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="62" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="63" operator="equal">
       <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="64" operator="equal">
-      <formula>"++"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE21:AG21">
-    <cfRule type="cellIs" dxfId="71" priority="81" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="71" priority="84" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="83" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="82" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="83" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="84" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="68" priority="81" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE13:AK13">
-    <cfRule type="cellIs" dxfId="67" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="116" operator="equal">
+      <formula>"++"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="113" operator="equal">
       <formula>"--"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="114" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="114" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="115" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="115" operator="equal">
       <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="116" operator="equal">
-      <formula>"++"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE19:AK19">
-    <cfRule type="cellIs" dxfId="63" priority="93" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="63" priority="96" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="95" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="94" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="95" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="96" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="93" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI14">
-    <cfRule type="cellIs" dxfId="59" priority="53" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="59" priority="56" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="55" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="54" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="55" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="56" priority="53" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI20">
@@ -8224,98 +8224,98 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI15:AK15">
-    <cfRule type="cellIs" dxfId="51" priority="49" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="51" priority="52" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="51" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="51" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="52" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="48" priority="49" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI21:AK21">
-    <cfRule type="cellIs" dxfId="47" priority="57" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="47" priority="60" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="59" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="58" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="59" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="60" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="44" priority="57" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5:AK5">
     <cfRule type="cellIs" dxfId="43" priority="45" operator="equal">
       <formula>"--"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="46" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="47" operator="equal">
       <formula>"+"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="48" operator="equal">
       <formula>"++"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="46" operator="equal">
+      <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO14">
-    <cfRule type="cellIs" dxfId="39" priority="33" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="39" priority="36" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="35" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="34" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="35" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="36" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="36" priority="33" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO20">
-    <cfRule type="cellIs" dxfId="35" priority="13" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="35" priority="16" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="15" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="14" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="15" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="16" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="32" priority="13" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO15:AQ15">
-    <cfRule type="cellIs" dxfId="31" priority="29" operator="equal">
-      <formula>"--"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="30" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
       <formula>"+"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="equal">
       <formula>"++"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO21:AQ21">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
-      <formula>"--"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="11" operator="equal">
       <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
       <formula>"++"</formula>
@@ -8336,25 +8336,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO19:AU19">
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS14">
-    <cfRule type="cellIs" dxfId="15" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="26" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
       <formula>"--"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="26" operator="equal">
-      <formula>"-"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="13" priority="27" operator="equal">
       <formula>"+"</formula>
@@ -8364,25 +8364,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS20">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+      <formula>"+"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
-      <formula>"+"</formula>
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"++"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS15:AU15">
-    <cfRule type="cellIs" dxfId="7" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="21" operator="equal">
       <formula>"--"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
-      <formula>"-"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="5" priority="23" operator="equal">
       <formula>"+"</formula>
@@ -8392,17 +8392,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS21:AU21">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"--"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"++"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"+"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"+"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>"++"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"--"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
